--- a/research/traditional_assets/database/data/sweden/sweden_power.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_power.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.06509012271182207</v>
+        <v>0.06499176705903574</v>
       </c>
       <c r="C2">
-        <v>245.2885670322195</v>
+        <v>244.0386434159243</v>
       </c>
       <c r="D2">
-        <v>245.2885670322195</v>
+        <v>246.5456434159243</v>
       </c>
       <c r="E2">
-        <v>-26.9</v>
+        <v>-24.393</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.507</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1439,28 +1439,28 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1261021</v>
       </c>
       <c r="N2">
-        <v>9.032222222222224</v>
+        <v>8.906120122222223</v>
       </c>
       <c r="O2">
-        <v>1.860637777777778</v>
+        <v>1.834660745177778</v>
       </c>
       <c r="P2">
-        <v>7.171584444444445</v>
+        <v>7.071459377044444</v>
       </c>
       <c r="Q2">
-        <v>12.36158444444445</v>
+        <v>12.26145937704445</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.06509012271182207</v>
+        <v>0.06524483339296538</v>
       </c>
       <c r="T2">
-        <v>0.4454993697880389</v>
+        <v>0.4490723647336117</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>71.626263339169</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.06499176705903574</v>
+        <v>0.06489341140624937</v>
       </c>
       <c r="C3">
-        <v>244.0386434159243</v>
+        <v>242.8016709235217</v>
       </c>
       <c r="D3">
-        <v>246.5456434159243</v>
+        <v>247.8156709235217</v>
       </c>
       <c r="E3">
-        <v>-24.393</v>
+        <v>-21.886</v>
       </c>
       <c r="F3">
-        <v>2.507</v>
+        <v>5.014</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1521,28 +1521,28 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M3">
-        <v>0.1261021</v>
+        <v>0.2522042</v>
       </c>
       <c r="N3">
-        <v>8.906120122222223</v>
+        <v>8.780018022222224</v>
       </c>
       <c r="O3">
-        <v>1.834660745177778</v>
+        <v>1.808683712577778</v>
       </c>
       <c r="P3">
-        <v>7.071459377044444</v>
+        <v>6.971334309644446</v>
       </c>
       <c r="Q3">
-        <v>12.26145937704445</v>
+        <v>12.16133430964445</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.06524483339296538</v>
+        <v>0.06540270143494833</v>
       </c>
       <c r="T3">
-        <v>0.4490723647336117</v>
+        <v>0.4527182779433797</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>71.626263339169</v>
+        <v>35.81313166958451</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.06489341140624937</v>
+        <v>0.064795055753463</v>
       </c>
       <c r="C4">
-        <v>242.8016709235217</v>
+        <v>241.5778507362437</v>
       </c>
       <c r="D4">
-        <v>247.8156709235217</v>
+        <v>249.0988507362437</v>
       </c>
       <c r="E4">
-        <v>-21.886</v>
+        <v>-19.379</v>
       </c>
       <c r="F4">
-        <v>5.014</v>
+        <v>7.521</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1603,28 +1603,28 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M4">
-        <v>0.2522042</v>
+        <v>0.3783063</v>
       </c>
       <c r="N4">
-        <v>8.780018022222224</v>
+        <v>8.653915922222224</v>
       </c>
       <c r="O4">
-        <v>1.808683712577778</v>
+        <v>1.782706679977778</v>
       </c>
       <c r="P4">
-        <v>6.971334309644446</v>
+        <v>6.871209242244445</v>
       </c>
       <c r="Q4">
-        <v>12.16133430964445</v>
+        <v>12.06120924224444</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.06540270143494833</v>
+        <v>0.0655638244881062</v>
       </c>
       <c r="T4">
-        <v>0.4527182779433797</v>
+        <v>0.4564393646213905</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>35.81313166958451</v>
+        <v>23.87542111305634</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.064795055753463</v>
+        <v>0.06469670010067667</v>
       </c>
       <c r="C5">
-        <v>241.5778507362437</v>
+        <v>240.3673882238451</v>
       </c>
       <c r="D5">
-        <v>249.0988507362437</v>
+        <v>250.3953882238451</v>
       </c>
       <c r="E5">
-        <v>-19.379</v>
+        <v>-16.872</v>
       </c>
       <c r="F5">
-        <v>7.521</v>
+        <v>10.028</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1685,28 +1685,28 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M5">
-        <v>0.3783063</v>
+        <v>0.5044084</v>
       </c>
       <c r="N5">
-        <v>8.653915922222224</v>
+        <v>8.527813822222225</v>
       </c>
       <c r="O5">
-        <v>1.782706679977778</v>
+        <v>1.756729647377778</v>
       </c>
       <c r="P5">
-        <v>6.871209242244445</v>
+        <v>6.771084174844447</v>
       </c>
       <c r="Q5">
-        <v>12.06120924224444</v>
+        <v>11.96108417484445</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.0655638244881062</v>
+        <v>0.0657283042715382</v>
       </c>
       <c r="T5">
-        <v>0.4564393646213905</v>
+        <v>0.4602379739385265</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>23.87542111305634</v>
+        <v>17.90656583479225</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.06469670010067667</v>
+        <v>0.06459834444789031</v>
       </c>
       <c r="C6">
-        <v>240.3673882238451</v>
+        <v>239.1704930541784</v>
       </c>
       <c r="D6">
-        <v>250.3953882238451</v>
+        <v>251.7054930541784</v>
       </c>
       <c r="E6">
-        <v>-16.872</v>
+        <v>-14.365</v>
       </c>
       <c r="F6">
-        <v>10.028</v>
+        <v>12.535</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1767,28 +1767,28 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M6">
-        <v>0.5044084</v>
+        <v>0.6305105000000001</v>
       </c>
       <c r="N6">
-        <v>8.527813822222225</v>
+        <v>8.401711722222224</v>
       </c>
       <c r="O6">
-        <v>1.756729647377778</v>
+        <v>1.730752614777778</v>
       </c>
       <c r="P6">
-        <v>6.771084174844447</v>
+        <v>6.670959107444446</v>
       </c>
       <c r="Q6">
-        <v>11.96108417484445</v>
+        <v>11.86095910744445</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0657283042715382</v>
+        <v>0.06589624678725296</v>
       </c>
       <c r="T6">
-        <v>0.4602379739385265</v>
+        <v>0.4641165539781286</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>17.90656583479225</v>
+        <v>14.3252526678338</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.06459834444789031</v>
+        <v>0.06457144879510396</v>
       </c>
       <c r="C7">
-        <v>239.1704930541784</v>
+        <v>237.0241356246852</v>
       </c>
       <c r="D7">
-        <v>251.7054930541784</v>
+        <v>252.0661356246852</v>
       </c>
       <c r="E7">
-        <v>-14.365</v>
+        <v>-11.858</v>
       </c>
       <c r="F7">
-        <v>12.535</v>
+        <v>15.042</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1849,45 +1849,45 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M7">
-        <v>0.6305105000000001</v>
+        <v>0.7791756000000001</v>
       </c>
       <c r="N7">
-        <v>8.401711722222224</v>
+        <v>8.253046622222223</v>
       </c>
       <c r="O7">
-        <v>1.730752614777778</v>
+        <v>1.700127604177778</v>
       </c>
       <c r="P7">
-        <v>6.670959107444446</v>
+        <v>6.552919018044445</v>
       </c>
       <c r="Q7">
-        <v>11.86095910744445</v>
+        <v>11.74291901804445</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.06589624678725296</v>
+        <v>0.06606776254798294</v>
       </c>
       <c r="T7">
-        <v>0.4641165539781286</v>
+        <v>0.4680776569972965</v>
       </c>
       <c r="U7">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V7">
         <v>0.206</v>
       </c>
       <c r="W7">
-        <v>0.0399382</v>
+        <v>0.0411292</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y7">
-        <v>14.3252526678338</v>
+        <v>11.5920239574009</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06457144879510396</v>
+        <v>0.06448500314231762</v>
       </c>
       <c r="C8">
-        <v>237.0241356246852</v>
+        <v>235.6833126637491</v>
       </c>
       <c r="D8">
-        <v>252.0661356246852</v>
+        <v>253.2323126637491</v>
       </c>
       <c r="E8">
-        <v>-11.858</v>
+        <v>-9.350999999999999</v>
       </c>
       <c r="F8">
-        <v>15.042</v>
+        <v>17.549</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1931,28 +1931,28 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M8">
-        <v>0.7791756</v>
+        <v>0.9090381999999999</v>
       </c>
       <c r="N8">
-        <v>8.253046622222223</v>
+        <v>8.123184022222224</v>
       </c>
       <c r="O8">
-        <v>1.700127604177778</v>
+        <v>1.673375908577778</v>
       </c>
       <c r="P8">
-        <v>6.552919018044445</v>
+        <v>6.449808113644446</v>
       </c>
       <c r="Q8">
-        <v>11.74291901804445</v>
+        <v>11.63980811364445</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.06606776254798294</v>
+        <v>0.06624296681969635</v>
       </c>
       <c r="T8">
-        <v>0.4680776569972965</v>
+        <v>0.4721239450276294</v>
       </c>
       <c r="U8">
         <v>0.0518</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>11.5920239574009</v>
+        <v>9.936020534915063</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0644850031423176</v>
+        <v>0.06450654148953126</v>
       </c>
       <c r="C9">
-        <v>235.6833126637493</v>
+        <v>232.8847459153515</v>
       </c>
       <c r="D9">
-        <v>253.2323126637493</v>
+        <v>252.9407459153515</v>
       </c>
       <c r="E9">
-        <v>-9.350999999999996</v>
+        <v>-6.843999999999998</v>
       </c>
       <c r="F9">
-        <v>17.549</v>
+        <v>20.056</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -2013,45 +2013,45 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M9">
-        <v>0.9090382000000001</v>
+        <v>1.072996</v>
       </c>
       <c r="N9">
-        <v>8.123184022222224</v>
+        <v>7.959226222222224</v>
       </c>
       <c r="O9">
-        <v>1.673375908577778</v>
+        <v>1.639600601777778</v>
       </c>
       <c r="P9">
-        <v>6.449808113644446</v>
+        <v>6.319625620444445</v>
       </c>
       <c r="Q9">
-        <v>11.63980811364445</v>
+        <v>11.50962562044445</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.06624296681969635</v>
+        <v>0.06642197987992528</v>
       </c>
       <c r="T9">
-        <v>0.4721239450276294</v>
+        <v>0.4762581958412304</v>
       </c>
       <c r="U9">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V9">
         <v>0.206</v>
       </c>
       <c r="W9">
-        <v>0.0411292</v>
+        <v>0.042479</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>9.936020534915059</v>
+        <v>8.417759453178039</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06450654148953126</v>
+        <v>0.0644907618367449</v>
       </c>
       <c r="C10">
-        <v>232.8847459153515</v>
+        <v>230.5912908302635</v>
       </c>
       <c r="D10">
-        <v>252.9407459153515</v>
+        <v>253.1542908302635</v>
       </c>
       <c r="E10">
-        <v>-6.843999999999998</v>
+        <v>-4.336999999999996</v>
       </c>
       <c r="F10">
-        <v>20.056</v>
+        <v>22.563</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2095,45 +2095,45 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M10">
-        <v>1.072996</v>
+        <v>1.2251709</v>
       </c>
       <c r="N10">
-        <v>7.959226222222224</v>
+        <v>7.807051322222224</v>
       </c>
       <c r="O10">
-        <v>1.639600601777778</v>
+        <v>1.608252572377778</v>
       </c>
       <c r="P10">
-        <v>6.319625620444445</v>
+        <v>6.198798749844445</v>
       </c>
       <c r="Q10">
-        <v>11.50962562044445</v>
+        <v>11.38879874984445</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.06642197987992528</v>
+        <v>0.06660492729312627</v>
       </c>
       <c r="T10">
-        <v>0.4762581958412304</v>
+        <v>0.4804833093100754</v>
       </c>
       <c r="U10">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V10">
         <v>0.206</v>
       </c>
       <c r="W10">
-        <v>0.042479</v>
+        <v>0.04311420000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y10">
-        <v>8.417759453178039</v>
+        <v>7.372214131287499</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0644907618367449</v>
+        <v>0.06442416618395855</v>
       </c>
       <c r="C11">
-        <v>230.5912908302635</v>
+        <v>228.9895112351388</v>
       </c>
       <c r="D11">
-        <v>253.1542908302635</v>
+        <v>254.0595112351388</v>
       </c>
       <c r="E11">
-        <v>-4.336999999999996</v>
+        <v>-1.829999999999998</v>
       </c>
       <c r="F11">
-        <v>22.563</v>
+        <v>25.07</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2177,28 +2177,28 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M11">
-        <v>1.2251709</v>
+        <v>1.361301</v>
       </c>
       <c r="N11">
-        <v>7.807051322222224</v>
+        <v>7.670921222222224</v>
       </c>
       <c r="O11">
-        <v>1.608252572377778</v>
+        <v>1.580209771777778</v>
       </c>
       <c r="P11">
-        <v>6.198798749844445</v>
+        <v>6.090711450444445</v>
       </c>
       <c r="Q11">
-        <v>11.38879874984445</v>
+        <v>11.28071145044445</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.06660492729312627</v>
+        <v>0.06679194020439838</v>
       </c>
       <c r="T11">
-        <v>0.4804833093100754</v>
+        <v>0.4848023141893392</v>
       </c>
       <c r="U11">
         <v>0.0543</v>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>7.372214131287499</v>
+        <v>6.634992718158749</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06442416618395855</v>
+        <v>0.0644449105311722</v>
       </c>
       <c r="C12">
-        <v>228.9895112351388</v>
+        <v>226.19984435373</v>
       </c>
       <c r="D12">
-        <v>254.0595112351388</v>
+        <v>253.77684435373</v>
       </c>
       <c r="E12">
-        <v>-1.829999999999995</v>
+        <v>0.6770000000000032</v>
       </c>
       <c r="F12">
-        <v>25.07</v>
+        <v>27.577</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2259,45 +2259,45 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M12">
-        <v>1.361301</v>
+        <v>1.5250081</v>
       </c>
       <c r="N12">
-        <v>7.670921222222224</v>
+        <v>7.507214122222224</v>
       </c>
       <c r="O12">
-        <v>1.580209771777778</v>
+        <v>1.546486109177778</v>
       </c>
       <c r="P12">
-        <v>6.090711450444445</v>
+        <v>5.960728013044445</v>
       </c>
       <c r="Q12">
-        <v>11.28071145044445</v>
+        <v>11.15072801304445</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.06679194020439838</v>
+        <v>0.06698315565300247</v>
       </c>
       <c r="T12">
-        <v>0.4848023141893392</v>
+        <v>0.4892183753580247</v>
       </c>
       <c r="U12">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V12">
         <v>0.206</v>
       </c>
       <c r="W12">
-        <v>0.04311420000000001</v>
+        <v>0.0439082</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y12">
-        <v>6.634992718158748</v>
+        <v>5.922737211836595</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0644449105311722</v>
+        <v>0.06438625487838584</v>
       </c>
       <c r="C13">
-        <v>226.19984435373</v>
+        <v>224.4937290163492</v>
       </c>
       <c r="D13">
-        <v>253.77684435373</v>
+        <v>254.5777290163492</v>
       </c>
       <c r="E13">
-        <v>0.6770000000000032</v>
+        <v>3.184000000000001</v>
       </c>
       <c r="F13">
-        <v>27.577</v>
+        <v>30.084</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2341,28 +2341,28 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M13">
-        <v>1.5250081</v>
+        <v>1.6636452</v>
       </c>
       <c r="N13">
-        <v>7.507214122222224</v>
+        <v>7.368577022222224</v>
       </c>
       <c r="O13">
-        <v>1.546486109177778</v>
+        <v>1.517926866577778</v>
       </c>
       <c r="P13">
-        <v>5.960728013044445</v>
+        <v>5.850650155644446</v>
       </c>
       <c r="Q13">
-        <v>11.15072801304445</v>
+        <v>11.04065015564445</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.06698315565300247</v>
+        <v>0.06717871690725663</v>
       </c>
       <c r="T13">
-        <v>0.4892183753580247</v>
+        <v>0.4937348015532711</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.922737211836595</v>
+        <v>5.429175777516879</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06438625487838584</v>
+        <v>0.06432759922559948</v>
       </c>
       <c r="C14">
-        <v>224.4937290163492</v>
+        <v>222.7926846449494</v>
       </c>
       <c r="D14">
-        <v>254.5777290163492</v>
+        <v>255.3836846449495</v>
       </c>
       <c r="E14">
-        <v>3.184000000000001</v>
+        <v>5.691000000000003</v>
       </c>
       <c r="F14">
-        <v>30.084</v>
+        <v>32.591</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2423,28 +2423,28 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M14">
-        <v>1.6636452</v>
+        <v>1.8022823</v>
       </c>
       <c r="N14">
-        <v>7.368577022222224</v>
+        <v>7.229939922222224</v>
       </c>
       <c r="O14">
-        <v>1.517926866577778</v>
+        <v>1.489367623977778</v>
       </c>
       <c r="P14">
-        <v>5.850650155644446</v>
+        <v>5.740572298244445</v>
       </c>
       <c r="Q14">
-        <v>11.04065015564445</v>
+        <v>10.93057229824445</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.06717871690725663</v>
+        <v>0.06737877382252815</v>
       </c>
       <c r="T14">
-        <v>0.4937348015532711</v>
+        <v>0.4983550536380634</v>
       </c>
       <c r="U14">
         <v>0.0553</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>5.429175777516879</v>
+        <v>5.011546871554042</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06432759922559948</v>
+        <v>0.06426894357281313</v>
       </c>
       <c r="C15">
-        <v>222.7926846449494</v>
+        <v>221.0967595542846</v>
       </c>
       <c r="D15">
-        <v>255.3836846449495</v>
+        <v>256.1947595542846</v>
       </c>
       <c r="E15">
-        <v>5.691000000000003</v>
+        <v>8.198000000000008</v>
       </c>
       <c r="F15">
-        <v>32.591</v>
+        <v>35.09800000000001</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2505,28 +2505,28 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M15">
-        <v>1.8022823</v>
+        <v>1.9409194</v>
       </c>
       <c r="N15">
-        <v>7.229939922222224</v>
+        <v>7.091302822222223</v>
       </c>
       <c r="O15">
-        <v>1.489367623977778</v>
+        <v>1.460808381377778</v>
       </c>
       <c r="P15">
-        <v>5.740572298244445</v>
+        <v>5.630494440844445</v>
       </c>
       <c r="Q15">
-        <v>10.93057229824445</v>
+        <v>10.82049444084445</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.06737877382252815</v>
+        <v>0.06758348322420131</v>
       </c>
       <c r="T15">
-        <v>0.4983550536380634</v>
+        <v>0.5030827534457579</v>
       </c>
       <c r="U15">
         <v>0.0553</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.011546871554042</v>
+        <v>4.65357923787161</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06426894357281313</v>
+        <v>0.06450803792002678</v>
       </c>
       <c r="C16">
-        <v>221.0967595542846</v>
+        <v>215.3155135292849</v>
       </c>
       <c r="D16">
-        <v>256.1947595542846</v>
+        <v>252.9205135292849</v>
       </c>
       <c r="E16">
-        <v>8.198000000000008</v>
+        <v>10.70500000000001</v>
       </c>
       <c r="F16">
-        <v>35.09800000000001</v>
+        <v>37.60500000000001</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2587,45 +2587,45 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M16">
-        <v>1.9409194</v>
+        <v>2.173569000000001</v>
       </c>
       <c r="N16">
-        <v>7.091302822222223</v>
+        <v>6.858653222222223</v>
       </c>
       <c r="O16">
-        <v>1.460808381377778</v>
+        <v>1.412882563777778</v>
       </c>
       <c r="P16">
-        <v>5.630494440844445</v>
+        <v>5.445770658444445</v>
       </c>
       <c r="Q16">
-        <v>10.82049444084445</v>
+        <v>10.63577065844445</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.06758348322420131</v>
+        <v>0.06779300931767857</v>
       </c>
       <c r="T16">
-        <v>0.5030827534457579</v>
+        <v>0.5079216932489276</v>
       </c>
       <c r="U16">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V16">
         <v>0.206</v>
       </c>
       <c r="W16">
-        <v>0.0439082</v>
+        <v>0.04589320000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>4.65357923787161</v>
+        <v>4.155479868466205</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06450803792002678</v>
+        <v>0.06491387226724042</v>
       </c>
       <c r="C17">
-        <v>215.3155135292849</v>
+        <v>207.4383912395687</v>
       </c>
       <c r="D17">
-        <v>252.9205135292849</v>
+        <v>247.5503912395687</v>
       </c>
       <c r="E17">
-        <v>10.70500000000001</v>
+        <v>13.212</v>
       </c>
       <c r="F17">
-        <v>37.605</v>
+        <v>40.112</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2669,45 +2669,45 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M17">
-        <v>2.173569000000001</v>
+        <v>2.4588656</v>
       </c>
       <c r="N17">
-        <v>6.858653222222223</v>
+        <v>6.573356622222223</v>
       </c>
       <c r="O17">
-        <v>1.412882563777778</v>
+        <v>1.354111464177778</v>
       </c>
       <c r="P17">
-        <v>5.445770658444445</v>
+        <v>5.219245158044446</v>
       </c>
       <c r="Q17">
-        <v>10.63577065844445</v>
+        <v>10.40924515804445</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.06779300931767857</v>
+        <v>0.06800752412766717</v>
       </c>
       <c r="T17">
-        <v>0.5079216932489276</v>
+        <v>0.5128758459045537</v>
       </c>
       <c r="U17">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V17">
         <v>0.206</v>
       </c>
       <c r="W17">
-        <v>0.04589320000000001</v>
+        <v>0.04867220000000001</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y17">
-        <v>4.155479868466205</v>
+        <v>3.6733289620312</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06491387226724042</v>
+        <v>0.06528080061445407</v>
       </c>
       <c r="C18">
-        <v>207.4383912395687</v>
+        <v>200.2686847262526</v>
       </c>
       <c r="D18">
-        <v>247.5503912395687</v>
+        <v>242.8876847262526</v>
       </c>
       <c r="E18">
-        <v>13.212</v>
+        <v>15.71900000000001</v>
       </c>
       <c r="F18">
-        <v>40.112</v>
+        <v>42.61900000000001</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2751,45 +2751,45 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M18">
-        <v>2.4588656</v>
+        <v>2.731877900000001</v>
       </c>
       <c r="N18">
-        <v>6.573356622222223</v>
+        <v>6.300344322222223</v>
       </c>
       <c r="O18">
-        <v>1.354111464177778</v>
+        <v>1.297870930377778</v>
       </c>
       <c r="P18">
-        <v>5.219245158044446</v>
+        <v>5.002473391844445</v>
       </c>
       <c r="Q18">
-        <v>10.40924515804445</v>
+        <v>10.19247339184444</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.06800752412766717</v>
+        <v>0.06822720796922177</v>
       </c>
       <c r="T18">
-        <v>0.5128758459045537</v>
+        <v>0.5179493757326045</v>
       </c>
       <c r="U18">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V18">
         <v>0.206</v>
       </c>
       <c r="W18">
-        <v>0.04867220000000001</v>
+        <v>0.05089540000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y18">
-        <v>3.6733289620312</v>
+        <v>3.306232032633018</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06528080061445407</v>
+        <v>0.06529201696166773</v>
       </c>
       <c r="C19">
-        <v>200.2686847262526</v>
+        <v>197.6219191693496</v>
       </c>
       <c r="D19">
-        <v>242.8876847262526</v>
+        <v>242.7479191693496</v>
       </c>
       <c r="E19">
-        <v>15.71900000000001</v>
+        <v>18.22600000000001</v>
       </c>
       <c r="F19">
-        <v>42.61900000000001</v>
+        <v>45.12600000000001</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2833,28 +2833,28 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M19">
-        <v>2.731877900000001</v>
+        <v>2.892576600000001</v>
       </c>
       <c r="N19">
-        <v>6.300344322222223</v>
+        <v>6.139645622222223</v>
       </c>
       <c r="O19">
-        <v>1.297870930377778</v>
+        <v>1.264766998177778</v>
       </c>
       <c r="P19">
-        <v>5.002473391844445</v>
+        <v>4.874878624044445</v>
       </c>
       <c r="Q19">
-        <v>10.19247339184444</v>
+        <v>10.06487862404445</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.06822720796922177</v>
+        <v>0.06845224995325332</v>
       </c>
       <c r="T19">
-        <v>0.5179493757326045</v>
+        <v>0.5231466501906078</v>
       </c>
       <c r="U19">
         <v>0.0641</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>3.306232032633018</v>
+        <v>3.122552475264517</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06529201696166773</v>
+        <v>0.06647994130888138</v>
       </c>
       <c r="C20">
-        <v>197.6219191693496</v>
+        <v>181.1706744004885</v>
       </c>
       <c r="D20">
-        <v>242.7479191693496</v>
+        <v>228.8036744004885</v>
       </c>
       <c r="E20">
-        <v>18.22600000000001</v>
+        <v>20.733</v>
       </c>
       <c r="F20">
-        <v>45.126</v>
+        <v>47.633</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2915,45 +2915,45 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M20">
-        <v>2.8925766</v>
+        <v>3.4248127</v>
       </c>
       <c r="N20">
-        <v>6.139645622222224</v>
+        <v>5.607409522222223</v>
       </c>
       <c r="O20">
-        <v>1.264766998177778</v>
+        <v>1.155126361577778</v>
       </c>
       <c r="P20">
-        <v>4.874878624044445</v>
+        <v>4.452283160644445</v>
       </c>
       <c r="Q20">
-        <v>10.06487862404445</v>
+        <v>9.642283160644446</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.06845224995325332</v>
+        <v>0.06868284852948317</v>
       </c>
       <c r="T20">
-        <v>0.5231466501906078</v>
+        <v>0.5284722524130062</v>
       </c>
       <c r="U20">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V20">
         <v>0.206</v>
       </c>
       <c r="W20">
-        <v>0.05089540000000001</v>
+        <v>0.05708860000000001</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>3.122552475264518</v>
+        <v>2.63728939752595</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06647994130888138</v>
+        <v>0.06655308965609502</v>
       </c>
       <c r="C21">
-        <v>181.1706744004885</v>
+        <v>177.8572108378985</v>
       </c>
       <c r="D21">
-        <v>228.8036744004885</v>
+        <v>227.9972108378986</v>
       </c>
       <c r="E21">
-        <v>20.733</v>
+        <v>23.24000000000001</v>
       </c>
       <c r="F21">
-        <v>47.633</v>
+        <v>50.14000000000001</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2997,28 +2997,28 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M21">
-        <v>3.4248127</v>
+        <v>3.605066000000001</v>
       </c>
       <c r="N21">
-        <v>5.607409522222223</v>
+        <v>5.427156222222223</v>
       </c>
       <c r="O21">
-        <v>1.155126361577778</v>
+        <v>1.117994181777778</v>
       </c>
       <c r="P21">
-        <v>4.452283160644445</v>
+        <v>4.309162040444445</v>
       </c>
       <c r="Q21">
-        <v>9.642283160644446</v>
+        <v>9.499162040444446</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.06868284852948317</v>
+        <v>0.06891921207011877</v>
       </c>
       <c r="T21">
-        <v>0.5284722524130062</v>
+        <v>0.5339309946909646</v>
       </c>
       <c r="U21">
         <v>0.07190000000000001</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.63728939752595</v>
+        <v>2.505424927649652</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06655308965609502</v>
+        <v>0.06727652400330866</v>
       </c>
       <c r="C22">
-        <v>177.8572108378985</v>
+        <v>167.6701498855938</v>
       </c>
       <c r="D22">
-        <v>227.9972108378986</v>
+        <v>220.3171498855938</v>
       </c>
       <c r="E22">
-        <v>23.24000000000001</v>
+        <v>25.74700000000001</v>
       </c>
       <c r="F22">
-        <v>50.14000000000001</v>
+        <v>52.64700000000001</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3079,45 +3079,45 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M22">
-        <v>3.605066000000001</v>
+        <v>3.990642600000001</v>
       </c>
       <c r="N22">
-        <v>5.427156222222223</v>
+        <v>5.041579622222223</v>
       </c>
       <c r="O22">
-        <v>1.117994181777778</v>
+        <v>1.038565402177778</v>
       </c>
       <c r="P22">
-        <v>4.309162040444445</v>
+        <v>4.003014220044445</v>
       </c>
       <c r="Q22">
-        <v>9.499162040444446</v>
+        <v>9.193014220044446</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.06891921207011877</v>
+        <v>0.06916155949785906</v>
       </c>
       <c r="T22">
-        <v>0.5339309946909646</v>
+        <v>0.5395279329759599</v>
       </c>
       <c r="U22">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V22">
         <v>0.206</v>
       </c>
       <c r="W22">
-        <v>0.05708860000000001</v>
+        <v>0.06018520000000001</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.505424927649652</v>
+        <v>2.263350324136324</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06727652400330866</v>
+        <v>0.06738063835052231</v>
       </c>
       <c r="C23">
-        <v>167.6701498855938</v>
+        <v>164.1002445225671</v>
       </c>
       <c r="D23">
-        <v>220.3171498855938</v>
+        <v>219.2542445225671</v>
       </c>
       <c r="E23">
-        <v>25.747</v>
+        <v>28.254</v>
       </c>
       <c r="F23">
-        <v>52.647</v>
+        <v>55.154</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3161,28 +3161,28 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M23">
-        <v>3.9906426</v>
+        <v>4.1806732</v>
       </c>
       <c r="N23">
-        <v>5.041579622222224</v>
+        <v>4.851549022222224</v>
       </c>
       <c r="O23">
-        <v>1.038565402177778</v>
+        <v>0.9994190985777781</v>
       </c>
       <c r="P23">
-        <v>4.003014220044445</v>
+        <v>3.852129923644446</v>
       </c>
       <c r="Q23">
-        <v>9.193014220044446</v>
+        <v>9.042129923644445</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.06916155949785906</v>
+        <v>0.06941012096220808</v>
       </c>
       <c r="T23">
-        <v>0.5395279329759599</v>
+        <v>0.545268382499032</v>
       </c>
       <c r="U23">
         <v>0.07580000000000001</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>2.263350324136324</v>
+        <v>2.160470763948309</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06738063835052231</v>
+        <v>0.06748475269773595</v>
       </c>
       <c r="C24">
-        <v>164.1002445225671</v>
+        <v>160.5405457502786</v>
       </c>
       <c r="D24">
-        <v>219.2542445225671</v>
+        <v>218.2015457502786</v>
       </c>
       <c r="E24">
-        <v>28.254</v>
+        <v>30.76100000000001</v>
       </c>
       <c r="F24">
-        <v>55.154</v>
+        <v>57.66100000000001</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3243,28 +3243,28 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M24">
-        <v>4.1806732</v>
+        <v>4.370703800000001</v>
       </c>
       <c r="N24">
-        <v>4.851549022222224</v>
+        <v>4.661518422222223</v>
       </c>
       <c r="O24">
-        <v>0.9994190985777781</v>
+        <v>0.960272794977778</v>
       </c>
       <c r="P24">
-        <v>3.852129923644446</v>
+        <v>3.701245627244445</v>
       </c>
       <c r="Q24">
-        <v>9.042129923644445</v>
+        <v>8.891245627244444</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.06941012096220808</v>
+        <v>0.06966513856848824</v>
       </c>
       <c r="T24">
-        <v>0.545268382499032</v>
+        <v>0.5511579346071189</v>
       </c>
       <c r="U24">
         <v>0.07580000000000001</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>2.160470763948309</v>
+        <v>2.066537252472296</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06748475269773595</v>
+        <v>0.07029481904494959</v>
       </c>
       <c r="C25">
-        <v>160.5405457502786</v>
+        <v>133.001279967965</v>
       </c>
       <c r="D25">
-        <v>218.2015457502786</v>
+        <v>193.169279967965</v>
       </c>
       <c r="E25">
-        <v>30.76100000000001</v>
+        <v>33.26800000000001</v>
       </c>
       <c r="F25">
-        <v>57.66100000000001</v>
+        <v>60.16800000000001</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3325,45 +3325,45 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M25">
-        <v>4.370703800000001</v>
+        <v>5.41512</v>
       </c>
       <c r="N25">
-        <v>4.661518422222223</v>
+        <v>3.617102222222224</v>
       </c>
       <c r="O25">
-        <v>0.960272794977778</v>
+        <v>0.7451230577777782</v>
       </c>
       <c r="P25">
-        <v>3.701245627244445</v>
+        <v>2.871979164444446</v>
       </c>
       <c r="Q25">
-        <v>8.891245627244444</v>
+        <v>8.061979164444447</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.06966513856848824</v>
+        <v>0.06992686716440737</v>
       </c>
       <c r="T25">
-        <v>0.5511579346071189</v>
+        <v>0.5572024749285767</v>
       </c>
       <c r="U25">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V25">
         <v>0.206</v>
       </c>
       <c r="W25">
-        <v>0.06018520000000001</v>
+        <v>0.07146</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y25">
-        <v>2.066537252472296</v>
+        <v>1.667963447203797</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07029481904494959</v>
+        <v>0.07051168139216324</v>
       </c>
       <c r="C26">
-        <v>133.001279967965</v>
+        <v>128.7990839673922</v>
       </c>
       <c r="D26">
-        <v>193.169279967965</v>
+        <v>191.4740839673922</v>
       </c>
       <c r="E26">
-        <v>33.268</v>
+        <v>35.77500000000001</v>
       </c>
       <c r="F26">
-        <v>60.168</v>
+        <v>62.675</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3407,28 +3407,28 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M26">
-        <v>5.41512</v>
+        <v>5.640750000000001</v>
       </c>
       <c r="N26">
-        <v>3.617102222222224</v>
+        <v>3.391472222222223</v>
       </c>
       <c r="O26">
-        <v>0.7451230577777782</v>
+        <v>0.698643277777778</v>
       </c>
       <c r="P26">
-        <v>2.871979164444446</v>
+        <v>2.692828944444445</v>
       </c>
       <c r="Q26">
-        <v>8.061979164444447</v>
+        <v>7.882828944444445</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.06992686716440737</v>
+        <v>0.070195575189551</v>
       </c>
       <c r="T26">
-        <v>0.5572024749285767</v>
+        <v>0.5634082029919398</v>
       </c>
       <c r="U26">
         <v>0.09</v>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>1.667963447203797</v>
+        <v>1.601244909315645</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07051168139216324</v>
+        <v>0.07072854373937688</v>
       </c>
       <c r="C27">
-        <v>128.7990839673922</v>
+        <v>124.6263822034275</v>
       </c>
       <c r="D27">
-        <v>191.4740839673922</v>
+        <v>189.8083822034275</v>
       </c>
       <c r="E27">
-        <v>35.77500000000001</v>
+        <v>38.282</v>
       </c>
       <c r="F27">
-        <v>62.675</v>
+        <v>65.182</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3489,28 +3489,28 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M27">
-        <v>5.640750000000001</v>
+        <v>5.86638</v>
       </c>
       <c r="N27">
-        <v>3.391472222222223</v>
+        <v>3.165842222222223</v>
       </c>
       <c r="O27">
-        <v>0.698643277777778</v>
+        <v>0.652163497777778</v>
       </c>
       <c r="P27">
-        <v>2.692828944444445</v>
+        <v>2.513678724444445</v>
       </c>
       <c r="Q27">
-        <v>7.882828944444445</v>
+        <v>7.703678724444446</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.070195575189551</v>
+        <v>0.07047154559375256</v>
       </c>
       <c r="T27">
-        <v>0.5634082029919398</v>
+        <v>0.569781653435394</v>
       </c>
       <c r="U27">
         <v>0.09</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>1.601244909315645</v>
+        <v>1.539658566649658</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07072854373937688</v>
+        <v>0.0839631014875073</v>
       </c>
       <c r="C28">
-        <v>124.6263822034275</v>
+        <v>56.29585378363218</v>
       </c>
       <c r="D28">
-        <v>189.8083822034275</v>
+        <v>123.9848537836322</v>
       </c>
       <c r="E28">
-        <v>38.282</v>
+        <v>40.78900000000001</v>
       </c>
       <c r="F28">
-        <v>65.182</v>
+        <v>67.68900000000001</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3571,45 +3571,45 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M28">
-        <v>5.86638</v>
+        <v>9.936745200000002</v>
       </c>
       <c r="N28">
-        <v>3.165842222222223</v>
+        <v>-0.9045229777777788</v>
       </c>
       <c r="O28">
-        <v>0.652163497777778</v>
+        <v>-0.1863317334222225</v>
       </c>
       <c r="P28">
-        <v>2.513678724444445</v>
+        <v>-0.7181912443555564</v>
       </c>
       <c r="Q28">
-        <v>7.703678724444446</v>
+        <v>4.471808755644444</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07047154559375256</v>
+        <v>0.07088886526326754</v>
       </c>
       <c r="T28">
-        <v>0.569781653435394</v>
+        <v>0.5794195210916294</v>
       </c>
       <c r="U28">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V28">
-        <v>0.206</v>
+        <v>0.1872482126016251</v>
       </c>
       <c r="W28">
-        <v>0.07146</v>
+        <v>0.1193119623900814</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y28">
-        <v>1.539658566649658</v>
+        <v>0.9089719058331315</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.0839631014875073</v>
+        <v>0.08497310148750731</v>
       </c>
       <c r="C29">
-        <v>56.29585378363218</v>
+        <v>50.59215253797244</v>
       </c>
       <c r="D29">
-        <v>123.9848537836322</v>
+        <v>120.7881525379725</v>
       </c>
       <c r="E29">
-        <v>40.78900000000001</v>
+        <v>43.29600000000001</v>
       </c>
       <c r="F29">
-        <v>67.68900000000001</v>
+        <v>70.19600000000001</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3653,37 +3653,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M29">
-        <v>9.936745200000002</v>
+        <v>10.3047728</v>
       </c>
       <c r="N29">
-        <v>-0.9045229777777788</v>
+        <v>-1.272550577777778</v>
       </c>
       <c r="O29">
-        <v>-0.1863317334222225</v>
+        <v>-0.2621454190222224</v>
       </c>
       <c r="P29">
-        <v>-0.7181912443555564</v>
+        <v>-1.010405158755556</v>
       </c>
       <c r="Q29">
-        <v>4.471808755644444</v>
+        <v>4.179594841244445</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07088886526326754</v>
+        <v>0.07123732172525737</v>
       </c>
       <c r="T29">
-        <v>0.5794195210916294</v>
+        <v>0.5874670144401243</v>
       </c>
       <c r="U29">
         <v>0.1468</v>
       </c>
       <c r="V29">
-        <v>0.1872482126016251</v>
+        <v>0.1805607764372814</v>
       </c>
       <c r="W29">
-        <v>0.1193119623900814</v>
+        <v>0.1202936780190071</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.9089719058331315</v>
+        <v>0.8765086234819482</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08497310148750731</v>
+        <v>0.0859831014875073</v>
       </c>
       <c r="C30">
-        <v>50.59215253797244</v>
+        <v>45.04914910500497</v>
       </c>
       <c r="D30">
-        <v>120.7881525379725</v>
+        <v>117.752149105005</v>
       </c>
       <c r="E30">
-        <v>43.29600000000001</v>
+        <v>45.80300000000002</v>
       </c>
       <c r="F30">
-        <v>70.19600000000001</v>
+        <v>72.70300000000002</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3735,37 +3735,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M30">
-        <v>10.3047728</v>
+        <v>10.6728004</v>
       </c>
       <c r="N30">
-        <v>-1.272550577777778</v>
+        <v>-1.64057817777778</v>
       </c>
       <c r="O30">
-        <v>-0.2621454190222224</v>
+        <v>-0.3379591046222227</v>
       </c>
       <c r="P30">
-        <v>-1.010405158755556</v>
+        <v>-1.302619073155557</v>
       </c>
       <c r="Q30">
-        <v>4.179594841244445</v>
+        <v>3.887380926844443</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07123732172525737</v>
+        <v>0.07159559386223283</v>
       </c>
       <c r="T30">
-        <v>0.5874670144401243</v>
+        <v>0.5957411977420979</v>
       </c>
       <c r="U30">
         <v>0.1468</v>
       </c>
       <c r="V30">
-        <v>0.1805607764372814</v>
+        <v>0.1743345427670303</v>
       </c>
       <c r="W30">
-        <v>0.1202936780190071</v>
+        <v>0.1212076891218</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.8765086234819482</v>
+        <v>0.8462841881894672</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08598310148750729</v>
+        <v>0.0869931014875073</v>
       </c>
       <c r="C31">
-        <v>45.04914910500504</v>
+        <v>39.6550231955339</v>
       </c>
       <c r="D31">
-        <v>117.752149105005</v>
+        <v>114.8650231955339</v>
       </c>
       <c r="E31">
-        <v>45.803</v>
+        <v>48.31000000000001</v>
       </c>
       <c r="F31">
-        <v>72.703</v>
+        <v>75.21000000000001</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3817,37 +3817,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M31">
-        <v>10.6728004</v>
+        <v>11.040828</v>
       </c>
       <c r="N31">
-        <v>-1.640578177777778</v>
+        <v>-2.008605777777779</v>
       </c>
       <c r="O31">
-        <v>-0.3379591046222223</v>
+        <v>-0.4137727902222226</v>
       </c>
       <c r="P31">
-        <v>-1.302619073155556</v>
+        <v>-1.594832987555557</v>
       </c>
       <c r="Q31">
-        <v>3.887380926844445</v>
+        <v>3.595167012444444</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07159559386223283</v>
+        <v>0.07196410234597903</v>
       </c>
       <c r="T31">
-        <v>0.5957411977420979</v>
+        <v>0.6042517862812707</v>
       </c>
       <c r="U31">
         <v>0.1468</v>
       </c>
       <c r="V31">
-        <v>0.1743345427670303</v>
+        <v>0.1685233913414626</v>
       </c>
       <c r="W31">
-        <v>0.1212076891218</v>
+        <v>0.1220607661510733</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.8462841881894674</v>
+        <v>0.8180747152498183</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0869931014875073</v>
+        <v>0.1050053702014535</v>
       </c>
       <c r="C32">
-        <v>39.6550231955339</v>
+        <v>2.202212425469298</v>
       </c>
       <c r="D32">
-        <v>114.8650231955339</v>
+        <v>79.9192124254693</v>
       </c>
       <c r="E32">
-        <v>48.31000000000001</v>
+        <v>50.817</v>
       </c>
       <c r="F32">
-        <v>75.21000000000001</v>
+        <v>77.717</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3899,45 +3899,45 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M32">
-        <v>11.040828</v>
+        <v>15.6055736</v>
       </c>
       <c r="N32">
-        <v>-2.008605777777779</v>
+        <v>-6.573351377777776</v>
       </c>
       <c r="O32">
-        <v>-0.4137727902222226</v>
+        <v>-1.354110383822222</v>
       </c>
       <c r="P32">
-        <v>-1.594832987555557</v>
+        <v>-5.219240993955554</v>
       </c>
       <c r="Q32">
-        <v>3.595167012444444</v>
+        <v>-0.02924099395555313</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07196410234597903</v>
+        <v>0.07272339182048038</v>
       </c>
       <c r="T32">
-        <v>0.6042517862812707</v>
+        <v>0.6217873399649048</v>
       </c>
       <c r="U32">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V32">
-        <v>0.1685233913414626</v>
+        <v>0.1192290540206595</v>
       </c>
       <c r="W32">
-        <v>0.1220607661510733</v>
+        <v>0.1768588059526516</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y32">
-        <v>0.8180747152498183</v>
+        <v>0.5787818156342696</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1050053702014535</v>
+        <v>0.1065553702014534</v>
       </c>
       <c r="C33">
-        <v>2.202212425469298</v>
+        <v>-2.343698354742102</v>
       </c>
       <c r="D33">
-        <v>79.9192124254693</v>
+        <v>77.8803016452579</v>
       </c>
       <c r="E33">
-        <v>50.817</v>
+        <v>53.32400000000001</v>
       </c>
       <c r="F33">
-        <v>77.717</v>
+        <v>80.224</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3981,37 +3981,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M33">
-        <v>15.6055736</v>
+        <v>16.1089792</v>
       </c>
       <c r="N33">
-        <v>-6.573351377777776</v>
+        <v>-7.076756977777777</v>
       </c>
       <c r="O33">
-        <v>-1.354110383822222</v>
+        <v>-1.457811937422222</v>
       </c>
       <c r="P33">
-        <v>-5.219240993955554</v>
+        <v>-5.618945040355555</v>
       </c>
       <c r="Q33">
-        <v>-0.02924099395555313</v>
+        <v>-0.4289450403555541</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07272339182048038</v>
+        <v>0.0731193240531345</v>
       </c>
       <c r="T33">
-        <v>0.6217873399649048</v>
+        <v>0.6309312714349768</v>
       </c>
       <c r="U33">
         <v>0.2008</v>
       </c>
       <c r="V33">
-        <v>0.1192290540206595</v>
+        <v>0.1155031460825139</v>
       </c>
       <c r="W33">
-        <v>0.1768588059526516</v>
+        <v>0.1776069682666312</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.5787818156342696</v>
+        <v>0.5606948838956987</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1065553702014534</v>
+        <v>0.1081053702014534</v>
       </c>
       <c r="C34">
-        <v>-2.343698354742102</v>
+        <v>-6.788163249980514</v>
       </c>
       <c r="D34">
-        <v>77.8803016452579</v>
+        <v>75.9428367500195</v>
       </c>
       <c r="E34">
-        <v>53.32400000000001</v>
+        <v>55.83100000000001</v>
       </c>
       <c r="F34">
-        <v>80.224</v>
+        <v>82.73100000000001</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4063,37 +4063,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M34">
-        <v>16.1089792</v>
+        <v>16.6123848</v>
       </c>
       <c r="N34">
-        <v>-7.076756977777777</v>
+        <v>-7.580162577777777</v>
       </c>
       <c r="O34">
-        <v>-1.457811937422222</v>
+        <v>-1.561513491022222</v>
       </c>
       <c r="P34">
-        <v>-5.618945040355555</v>
+        <v>-6.018649086755556</v>
       </c>
       <c r="Q34">
-        <v>-0.4289450403555541</v>
+        <v>-0.8286490867555552</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.0731193240531345</v>
+        <v>0.07352707515840516</v>
       </c>
       <c r="T34">
-        <v>0.6309312714349768</v>
+        <v>0.6403481560832601</v>
       </c>
       <c r="U34">
         <v>0.2008</v>
       </c>
       <c r="V34">
-        <v>0.1155031460825139</v>
+        <v>0.1120030507466802</v>
       </c>
       <c r="W34">
-        <v>0.1776069682666312</v>
+        <v>0.1783097874100666</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.5606948838956987</v>
+        <v>0.5437041298382532</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1081053702014534</v>
+        <v>0.1096553702014535</v>
       </c>
       <c r="C35">
-        <v>-6.788163249980514</v>
+        <v>-11.13856963210888</v>
       </c>
       <c r="D35">
-        <v>75.9428367500195</v>
+        <v>74.09943036789113</v>
       </c>
       <c r="E35">
-        <v>55.83100000000001</v>
+        <v>58.33800000000002</v>
       </c>
       <c r="F35">
-        <v>82.73100000000001</v>
+        <v>85.23800000000001</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4145,37 +4145,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M35">
-        <v>16.6123848</v>
+        <v>17.1157904</v>
       </c>
       <c r="N35">
-        <v>-7.580162577777777</v>
+        <v>-8.083568177777778</v>
       </c>
       <c r="O35">
-        <v>-1.561513491022222</v>
+        <v>-1.665215044622222</v>
       </c>
       <c r="P35">
-        <v>-6.018649086755556</v>
+        <v>-6.418353133155556</v>
       </c>
       <c r="Q35">
-        <v>-0.8286490867555552</v>
+        <v>-1.228353133155555</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.07352707515840516</v>
+        <v>0.07394718235777493</v>
       </c>
       <c r="T35">
-        <v>0.6403481560832601</v>
+        <v>0.6500504008724004</v>
       </c>
       <c r="U35">
         <v>0.2008</v>
       </c>
       <c r="V35">
-        <v>0.1120030507466802</v>
+        <v>0.1087088433717778</v>
       </c>
       <c r="W35">
-        <v>0.1783097874100666</v>
+        <v>0.178971264250947</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.5437041298382532</v>
+        <v>0.5277128319018339</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1096553702014535</v>
+        <v>0.1112053702014534</v>
       </c>
       <c r="C36">
-        <v>-11.13856963210888</v>
+        <v>-15.40160459860284</v>
       </c>
       <c r="D36">
-        <v>74.09943036789113</v>
+        <v>72.34339540139717</v>
       </c>
       <c r="E36">
-        <v>58.33800000000002</v>
+        <v>60.84500000000002</v>
       </c>
       <c r="F36">
-        <v>85.23800000000001</v>
+        <v>87.74500000000002</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4227,37 +4227,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M36">
-        <v>17.1157904</v>
+        <v>17.61919600000001</v>
       </c>
       <c r="N36">
-        <v>-8.083568177777778</v>
+        <v>-8.586973777777782</v>
       </c>
       <c r="O36">
-        <v>-1.665215044622222</v>
+        <v>-1.768916598222223</v>
       </c>
       <c r="P36">
-        <v>-6.418353133155556</v>
+        <v>-6.818057179555559</v>
       </c>
       <c r="Q36">
-        <v>-1.228353133155555</v>
+        <v>-1.628057179555559</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.07394718235777493</v>
+        <v>0.07438021593250993</v>
       </c>
       <c r="T36">
-        <v>0.6500504008724004</v>
+        <v>0.6600511762704373</v>
       </c>
       <c r="U36">
         <v>0.2008</v>
       </c>
       <c r="V36">
-        <v>0.1087088433717778</v>
+        <v>0.1056028764182984</v>
       </c>
       <c r="W36">
-        <v>0.178971264250947</v>
+        <v>0.1795949424152057</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.5277128319018339</v>
+        <v>0.5126353224189243</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1112053702014534</v>
+        <v>0.1254611987953855</v>
       </c>
       <c r="C37">
-        <v>-15.40160459860284</v>
+        <v>-30.85487028805554</v>
       </c>
       <c r="D37">
-        <v>72.34339540139717</v>
+        <v>59.39712971194449</v>
       </c>
       <c r="E37">
-        <v>60.84500000000002</v>
+        <v>63.35200000000003</v>
       </c>
       <c r="F37">
-        <v>87.74500000000002</v>
+        <v>90.25200000000002</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4309,45 +4309,45 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M37">
-        <v>17.61919600000001</v>
+        <v>21.28142160000001</v>
       </c>
       <c r="N37">
-        <v>-8.586973777777782</v>
+        <v>-12.24919937777778</v>
       </c>
       <c r="O37">
-        <v>-1.768916598222223</v>
+        <v>-2.523335071822223</v>
       </c>
       <c r="P37">
-        <v>-6.818057179555559</v>
+        <v>-9.725864305955557</v>
       </c>
       <c r="Q37">
-        <v>-1.628057179555559</v>
+        <v>-4.535864305955557</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.07438021593250993</v>
+        <v>0.07499213898447418</v>
       </c>
       <c r="T37">
-        <v>0.6600511762704373</v>
+        <v>0.6741833483712285</v>
       </c>
       <c r="U37">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.1056028764182984</v>
+        <v>0.08743014506971554</v>
       </c>
       <c r="W37">
-        <v>0.1795949424152057</v>
+        <v>0.2151839717925611</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y37">
-        <v>0.5126353224189243</v>
+        <v>0.4244181799500754</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1254611987953855</v>
+        <v>0.1273611987953855</v>
       </c>
       <c r="C38">
-        <v>-30.85487028805552</v>
+        <v>-34.74554963705349</v>
       </c>
       <c r="D38">
-        <v>59.39712971194449</v>
+        <v>58.01345036294651</v>
       </c>
       <c r="E38">
-        <v>63.35200000000001</v>
+        <v>65.85900000000001</v>
       </c>
       <c r="F38">
-        <v>90.25200000000001</v>
+        <v>92.759</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4391,37 +4391,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M38">
-        <v>21.2814216</v>
+        <v>21.8725722</v>
       </c>
       <c r="N38">
-        <v>-12.24919937777778</v>
+        <v>-12.84034997777778</v>
       </c>
       <c r="O38">
-        <v>-2.523335071822222</v>
+        <v>-2.645112095422222</v>
       </c>
       <c r="P38">
-        <v>-9.725864305955556</v>
+        <v>-10.19523788235555</v>
       </c>
       <c r="Q38">
-        <v>-4.535864305955555</v>
+        <v>-5.005237882355554</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.07499213898447418</v>
+        <v>0.07545550626994203</v>
       </c>
       <c r="T38">
-        <v>0.6741833483712285</v>
+        <v>0.6848846713612481</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.08743014506971555</v>
+        <v>0.08506716817593947</v>
       </c>
       <c r="W38">
-        <v>0.2151839717925611</v>
+        <v>0.2157411617441135</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.4244181799500755</v>
+        <v>0.4129474183298032</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1273611987953855</v>
+        <v>0.1292611987953855</v>
       </c>
       <c r="C39">
-        <v>-34.74554963705349</v>
+        <v>-38.57322987266609</v>
       </c>
       <c r="D39">
-        <v>58.01345036294651</v>
+        <v>56.69277012733392</v>
       </c>
       <c r="E39">
-        <v>65.85900000000001</v>
+        <v>68.36600000000001</v>
       </c>
       <c r="F39">
-        <v>92.759</v>
+        <v>95.26600000000001</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4473,37 +4473,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M39">
-        <v>21.8725722</v>
+        <v>22.4637228</v>
       </c>
       <c r="N39">
-        <v>-12.84034997777778</v>
+        <v>-13.43150057777778</v>
       </c>
       <c r="O39">
-        <v>-2.645112095422222</v>
+        <v>-2.766889119022223</v>
       </c>
       <c r="P39">
-        <v>-10.19523788235555</v>
+        <v>-10.66461145875556</v>
       </c>
       <c r="Q39">
-        <v>-5.005237882355554</v>
+        <v>-5.474611458755557</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.07545550626994203</v>
+        <v>0.07593382088719916</v>
       </c>
       <c r="T39">
-        <v>0.6848846713612481</v>
+        <v>0.6959311983186875</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.08506716817593947</v>
+        <v>0.08282855848709894</v>
       </c>
       <c r="W39">
-        <v>0.2157411617441135</v>
+        <v>0.2162690259087421</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.4129474183298032</v>
+        <v>0.4020803810053346</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1292611987953855</v>
+        <v>0.1311611987953855</v>
       </c>
       <c r="C40">
-        <v>-38.57322987266609</v>
+        <v>-42.34211776508118</v>
       </c>
       <c r="D40">
-        <v>56.69277012733392</v>
+        <v>55.43088223491883</v>
       </c>
       <c r="E40">
-        <v>68.36600000000001</v>
+        <v>70.87300000000002</v>
       </c>
       <c r="F40">
-        <v>95.26600000000001</v>
+        <v>97.77300000000001</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4555,37 +4555,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M40">
-        <v>22.4637228</v>
+        <v>23.0548734</v>
       </c>
       <c r="N40">
-        <v>-13.43150057777778</v>
+        <v>-14.02265117777778</v>
       </c>
       <c r="O40">
-        <v>-2.766889119022223</v>
+        <v>-2.888666142622223</v>
       </c>
       <c r="P40">
-        <v>-10.66461145875556</v>
+        <v>-11.13398503515556</v>
       </c>
       <c r="Q40">
-        <v>-5.474611458755557</v>
+        <v>-5.943985035155555</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.07593382088719916</v>
+        <v>0.07642781795092374</v>
       </c>
       <c r="T40">
-        <v>0.6959311983186875</v>
+        <v>0.7073399064878464</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.08282855848709894</v>
+        <v>0.08070474929512204</v>
       </c>
       <c r="W40">
-        <v>0.2162690259087421</v>
+        <v>0.2167698201162102</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.4020803810053346</v>
+        <v>0.3917706276462235</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1311611987953855</v>
+        <v>0.1330611987953855</v>
       </c>
       <c r="C41">
-        <v>-42.34211776508118</v>
+        <v>-46.05605369651735</v>
       </c>
       <c r="D41">
-        <v>55.43088223491883</v>
+        <v>54.22394630348266</v>
       </c>
       <c r="E41">
-        <v>70.87300000000002</v>
+        <v>73.38000000000002</v>
       </c>
       <c r="F41">
-        <v>97.77300000000001</v>
+        <v>100.28</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4637,37 +4637,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M41">
-        <v>23.0548734</v>
+        <v>23.646024</v>
       </c>
       <c r="N41">
-        <v>-14.02265117777778</v>
+        <v>-14.61380177777778</v>
       </c>
       <c r="O41">
-        <v>-2.888666142622223</v>
+        <v>-3.010443166222223</v>
       </c>
       <c r="P41">
-        <v>-11.13398503515556</v>
+        <v>-11.60335861155556</v>
       </c>
       <c r="Q41">
-        <v>-5.943985035155555</v>
+        <v>-6.413358611555556</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.07642781795092374</v>
+        <v>0.07693828158343914</v>
       </c>
       <c r="T41">
-        <v>0.7073399064878464</v>
+        <v>0.7191289049293105</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.08070474929512204</v>
+        <v>0.078687130562744</v>
       </c>
       <c r="W41">
-        <v>0.2167698201162102</v>
+        <v>0.217245574613305</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3917706276462235</v>
+        <v>0.3819763619550679</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1330611987953855</v>
+        <v>0.1349611987953855</v>
       </c>
       <c r="C42">
-        <v>-46.05605369651735</v>
+        <v>-49.71855069934536</v>
       </c>
       <c r="D42">
-        <v>54.22394630348266</v>
+        <v>53.06844930065466</v>
       </c>
       <c r="E42">
-        <v>73.38000000000002</v>
+        <v>75.88700000000003</v>
       </c>
       <c r="F42">
-        <v>100.28</v>
+        <v>102.787</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4719,37 +4719,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M42">
-        <v>23.646024</v>
+        <v>24.23717460000001</v>
       </c>
       <c r="N42">
-        <v>-14.61380177777778</v>
+        <v>-15.20495237777778</v>
       </c>
       <c r="O42">
-        <v>-3.010443166222223</v>
+        <v>-3.132220189822223</v>
       </c>
       <c r="P42">
-        <v>-11.60335861155556</v>
+        <v>-12.07273218795556</v>
       </c>
       <c r="Q42">
-        <v>-6.413358611555556</v>
+        <v>-6.882732187955559</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.07693828158343914</v>
+        <v>0.07746604906790421</v>
       </c>
       <c r="T42">
-        <v>0.7191289049293105</v>
+        <v>0.7313175304365869</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.078687130562744</v>
+        <v>0.07676793225633559</v>
       </c>
       <c r="W42">
-        <v>0.217245574613305</v>
+        <v>0.2176981215739561</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3819763619550679</v>
+        <v>0.3726598653220174</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1349611987953855</v>
+        <v>0.1368611987953855</v>
       </c>
       <c r="C43">
-        <v>-49.71855069934536</v>
+        <v>-53.33282860700621</v>
       </c>
       <c r="D43">
-        <v>53.06844930065466</v>
+        <v>51.9611713929938</v>
       </c>
       <c r="E43">
-        <v>75.88700000000003</v>
+        <v>78.39400000000001</v>
       </c>
       <c r="F43">
-        <v>102.787</v>
+        <v>105.294</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4801,37 +4801,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M43">
-        <v>24.23717460000001</v>
+        <v>24.8283252</v>
       </c>
       <c r="N43">
-        <v>-15.20495237777778</v>
+        <v>-15.79610297777778</v>
       </c>
       <c r="O43">
-        <v>-3.132220189822223</v>
+        <v>-3.253997213422223</v>
       </c>
       <c r="P43">
-        <v>-12.07273218795556</v>
+        <v>-12.54210576435556</v>
       </c>
       <c r="Q43">
-        <v>-6.882732187955559</v>
+        <v>-7.352105764355556</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.07746604906790421</v>
+        <v>0.07801201543114394</v>
       </c>
       <c r="T43">
-        <v>0.7313175304365869</v>
+        <v>0.7439264533751487</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.07676793225633559</v>
+        <v>0.07494012434547047</v>
       </c>
       <c r="W43">
-        <v>0.2176981215739561</v>
+        <v>0.2181291186793381</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3726598653220174</v>
+        <v>0.363787011385779</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1368611987953855</v>
+        <v>0.1387611987953855</v>
       </c>
       <c r="C44">
-        <v>-53.33282860700617</v>
+        <v>-56.90184401694072</v>
       </c>
       <c r="D44">
-        <v>51.96117139299383</v>
+        <v>50.89915598305928</v>
       </c>
       <c r="E44">
-        <v>78.39400000000001</v>
+        <v>80.90100000000001</v>
       </c>
       <c r="F44">
-        <v>105.294</v>
+        <v>107.801</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4883,37 +4883,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M44">
-        <v>24.8283252</v>
+        <v>25.4194758</v>
       </c>
       <c r="N44">
-        <v>-15.79610297777778</v>
+        <v>-16.38725357777778</v>
       </c>
       <c r="O44">
-        <v>-3.253997213422223</v>
+        <v>-3.375774237022222</v>
       </c>
       <c r="P44">
-        <v>-12.54210576435556</v>
+        <v>-13.01147934075555</v>
       </c>
       <c r="Q44">
-        <v>-7.352105764355556</v>
+        <v>-7.821479340755555</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.07801201543114393</v>
+        <v>0.0785771385088833</v>
       </c>
       <c r="T44">
-        <v>0.7439264533751486</v>
+        <v>0.756977794662432</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.07494012434547047</v>
+        <v>0.07319733075604093</v>
       </c>
       <c r="W44">
-        <v>0.2181291186793381</v>
+        <v>0.2185400694077256</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.363787011385779</v>
+        <v>0.3553268483302957</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1387611987953855</v>
+        <v>0.1406611987953855</v>
       </c>
       <c r="C45">
-        <v>-56.90184401694072</v>
+        <v>-60.42831665270631</v>
       </c>
       <c r="D45">
-        <v>50.89915598305928</v>
+        <v>49.8796833472937</v>
       </c>
       <c r="E45">
-        <v>80.90100000000001</v>
+        <v>83.40800000000002</v>
       </c>
       <c r="F45">
-        <v>107.801</v>
+        <v>110.308</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4965,37 +4965,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M45">
-        <v>25.4194758</v>
+        <v>26.0106264</v>
       </c>
       <c r="N45">
-        <v>-16.38725357777778</v>
+        <v>-16.97840417777778</v>
       </c>
       <c r="O45">
-        <v>-3.375774237022222</v>
+        <v>-3.497551260622223</v>
       </c>
       <c r="P45">
-        <v>-13.01147934075555</v>
+        <v>-13.48085291715556</v>
       </c>
       <c r="Q45">
-        <v>-7.821479340755555</v>
+        <v>-8.290852917155554</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.0785771385088833</v>
+        <v>0.07916244455368479</v>
       </c>
       <c r="T45">
-        <v>0.756977794662432</v>
+        <v>0.7704952552814041</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.07319733075604093</v>
+        <v>0.07153375505703999</v>
       </c>
       <c r="W45">
-        <v>0.2185400694077256</v>
+        <v>0.21893234055755</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3553268483302957</v>
+        <v>0.3472512381409708</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1406611987953855</v>
+        <v>0.1425611987953855</v>
       </c>
       <c r="C46">
-        <v>-60.42831665270631</v>
+        <v>-63.9147526202191</v>
       </c>
       <c r="D46">
-        <v>49.8796833472937</v>
+        <v>48.90024737978091</v>
       </c>
       <c r="E46">
-        <v>83.40800000000002</v>
+        <v>85.91500000000002</v>
       </c>
       <c r="F46">
-        <v>110.308</v>
+        <v>112.815</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5047,37 +5047,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M46">
-        <v>26.0106264</v>
+        <v>26.60177700000001</v>
       </c>
       <c r="N46">
-        <v>-16.97840417777778</v>
+        <v>-17.56955477777778</v>
       </c>
       <c r="O46">
-        <v>-3.497551260622223</v>
+        <v>-3.619328284222223</v>
       </c>
       <c r="P46">
-        <v>-13.48085291715556</v>
+        <v>-13.95022649355556</v>
       </c>
       <c r="Q46">
-        <v>-8.290852917155554</v>
+        <v>-8.760226493555557</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.07916244455368479</v>
+        <v>0.07976903445466088</v>
       </c>
       <c r="T46">
-        <v>0.7704952552814041</v>
+        <v>0.7845042599228841</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.07153375505703999</v>
+        <v>0.06994411605577243</v>
       </c>
       <c r="W46">
-        <v>0.21893234055755</v>
+        <v>0.2193071774340489</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.3472512381409708</v>
+        <v>0.3395345439600603</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1425611987953855</v>
+        <v>0.1444611987953855</v>
       </c>
       <c r="C47">
-        <v>-63.9147526202191</v>
+        <v>-67.36346497680897</v>
       </c>
       <c r="D47">
-        <v>48.90024737978091</v>
+        <v>47.95853502319105</v>
       </c>
       <c r="E47">
-        <v>85.91500000000002</v>
+        <v>88.42200000000003</v>
       </c>
       <c r="F47">
-        <v>112.815</v>
+        <v>115.322</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5129,37 +5129,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M47">
-        <v>26.60177700000001</v>
+        <v>27.1929276</v>
       </c>
       <c r="N47">
-        <v>-17.56955477777778</v>
+        <v>-18.16070537777778</v>
       </c>
       <c r="O47">
-        <v>-3.619328284222223</v>
+        <v>-3.741105307822223</v>
       </c>
       <c r="P47">
-        <v>-13.95022649355556</v>
+        <v>-14.41960006995556</v>
       </c>
       <c r="Q47">
-        <v>-8.760226493555557</v>
+        <v>-9.229600069955556</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.07976903445466088</v>
+        <v>0.0803980906482657</v>
       </c>
       <c r="T47">
-        <v>0.7845042599228841</v>
+        <v>0.7990321165881227</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.06994411605577243</v>
+        <v>0.06842359179369042</v>
       </c>
       <c r="W47">
-        <v>0.2193071774340489</v>
+        <v>0.2196657170550478</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.3395345439600603</v>
+        <v>0.3321533582217981</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1444611987953855</v>
+        <v>0.1463611987953855</v>
       </c>
       <c r="C48">
-        <v>-67.36346497680897</v>
+        <v>-70.77659196848766</v>
       </c>
       <c r="D48">
-        <v>47.95853502319105</v>
+        <v>47.05240803151236</v>
       </c>
       <c r="E48">
-        <v>88.42200000000003</v>
+        <v>90.92900000000003</v>
       </c>
       <c r="F48">
-        <v>115.322</v>
+        <v>117.829</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5211,37 +5211,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M48">
-        <v>27.1929276</v>
+        <v>27.78407820000001</v>
       </c>
       <c r="N48">
-        <v>-18.16070537777778</v>
+        <v>-18.75185597777778</v>
       </c>
       <c r="O48">
-        <v>-3.741105307822223</v>
+        <v>-3.862882331422224</v>
       </c>
       <c r="P48">
-        <v>-14.41960006995556</v>
+        <v>-14.88897364635556</v>
       </c>
       <c r="Q48">
-        <v>-9.229600069955556</v>
+        <v>-9.698973646355558</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.0803980906482657</v>
+        <v>0.08105088481144053</v>
       </c>
       <c r="T48">
-        <v>0.7990321165881227</v>
+        <v>0.8141081942595967</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.06842359179369042</v>
+        <v>0.066967770691697</v>
       </c>
       <c r="W48">
-        <v>0.2196657170550478</v>
+        <v>0.2200089996708978</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3321533582217981</v>
+        <v>0.3250862654936748</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1463611987953855</v>
+        <v>0.1482611987953855</v>
       </c>
       <c r="C49">
-        <v>-70.77659196848766</v>
+        <v>-74.15611323810899</v>
       </c>
       <c r="D49">
-        <v>47.05240803151236</v>
+        <v>46.17988676189102</v>
       </c>
       <c r="E49">
-        <v>90.92900000000003</v>
+        <v>93.43600000000001</v>
       </c>
       <c r="F49">
-        <v>117.829</v>
+        <v>120.336</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5293,37 +5293,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M49">
-        <v>27.78407820000001</v>
+        <v>28.37522880000001</v>
       </c>
       <c r="N49">
-        <v>-18.75185597777778</v>
+        <v>-19.34300657777778</v>
       </c>
       <c r="O49">
-        <v>-3.862882331422224</v>
+        <v>-3.984659355022223</v>
       </c>
       <c r="P49">
-        <v>-14.88897364635556</v>
+        <v>-15.35834722275556</v>
       </c>
       <c r="Q49">
-        <v>-9.698973646355558</v>
+        <v>-10.16834722275556</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.08105088481144053</v>
+        <v>0.08172878644242978</v>
       </c>
       <c r="T49">
-        <v>0.8141081942595967</v>
+        <v>0.8297641210722814</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.066967770691697</v>
+        <v>0.06557260880228666</v>
       </c>
       <c r="W49">
-        <v>0.2200089996708978</v>
+        <v>0.2203379788444208</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3250862654936748</v>
+        <v>0.3183136349625566</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1482611987953855</v>
+        <v>0.1501611987953855</v>
       </c>
       <c r="C50">
-        <v>-74.15611323810896</v>
+        <v>-77.50386426301452</v>
       </c>
       <c r="D50">
-        <v>46.17988676189105</v>
+        <v>45.33913573698548</v>
       </c>
       <c r="E50">
-        <v>93.43600000000001</v>
+        <v>95.94300000000001</v>
       </c>
       <c r="F50">
-        <v>120.336</v>
+        <v>122.843</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5375,37 +5375,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M50">
-        <v>28.3752288</v>
+        <v>28.9663794</v>
       </c>
       <c r="N50">
-        <v>-19.34300657777778</v>
+        <v>-19.93415717777778</v>
       </c>
       <c r="O50">
-        <v>-3.984659355022222</v>
+        <v>-4.106436378622223</v>
       </c>
       <c r="P50">
-        <v>-15.35834722275556</v>
+        <v>-15.82772079915555</v>
       </c>
       <c r="Q50">
-        <v>-10.16834722275556</v>
+        <v>-10.63772079915555</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.08172878644242977</v>
+        <v>0.08243327245110486</v>
       </c>
       <c r="T50">
-        <v>0.8297641210722813</v>
+        <v>0.8460340057991887</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.06557260880228667</v>
+        <v>0.06423439229611755</v>
       </c>
       <c r="W50">
-        <v>0.2203379788444208</v>
+        <v>0.2206535302965755</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.3183136349625566</v>
+        <v>0.3118174383306677</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1501611987953855</v>
+        <v>0.1520611987953855</v>
       </c>
       <c r="C51">
-        <v>-77.50386426301452</v>
+        <v>-80.82154924376795</v>
       </c>
       <c r="D51">
-        <v>45.33913573698548</v>
+        <v>44.52845075623205</v>
       </c>
       <c r="E51">
-        <v>95.94300000000001</v>
+        <v>98.45000000000002</v>
       </c>
       <c r="F51">
-        <v>122.843</v>
+        <v>125.35</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5457,37 +5457,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M51">
-        <v>28.9663794</v>
+        <v>29.55753</v>
       </c>
       <c r="N51">
-        <v>-19.93415717777778</v>
+        <v>-20.52530777777778</v>
       </c>
       <c r="O51">
-        <v>-4.106436378622223</v>
+        <v>-4.228213402222223</v>
       </c>
       <c r="P51">
-        <v>-15.82772079915555</v>
+        <v>-16.29709437555556</v>
       </c>
       <c r="Q51">
-        <v>-10.63772079915555</v>
+        <v>-11.10709437555555</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.08243327245110486</v>
+        <v>0.08316593790012697</v>
       </c>
       <c r="T51">
-        <v>0.8460340057991887</v>
+        <v>0.8629546859151725</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.06423439229611755</v>
+        <v>0.0629497044501952</v>
       </c>
       <c r="W51">
-        <v>0.2206535302965755</v>
+        <v>0.220956459690644</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3118174383306677</v>
+        <v>0.3055810895640543</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1520611987953855</v>
+        <v>0.1539611987953855</v>
       </c>
       <c r="C52">
-        <v>-80.82154924376795</v>
+        <v>-84.11075263443942</v>
       </c>
       <c r="D52">
-        <v>44.52845075623205</v>
+        <v>43.74624736556058</v>
       </c>
       <c r="E52">
-        <v>98.45000000000002</v>
+        <v>100.957</v>
       </c>
       <c r="F52">
-        <v>125.35</v>
+        <v>127.857</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5539,37 +5539,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M52">
-        <v>29.55753</v>
+        <v>30.14868060000001</v>
       </c>
       <c r="N52">
-        <v>-20.52530777777778</v>
+        <v>-21.11645837777778</v>
       </c>
       <c r="O52">
-        <v>-4.228213402222223</v>
+        <v>-4.349990425822224</v>
       </c>
       <c r="P52">
-        <v>-16.29709437555556</v>
+        <v>-16.76646795195556</v>
       </c>
       <c r="Q52">
-        <v>-11.10709437555555</v>
+        <v>-11.57646795195556</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.08316593790012697</v>
+        <v>0.08392850806135405</v>
       </c>
       <c r="T52">
-        <v>0.8629546859151725</v>
+        <v>0.8805660060358904</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0629497044501952</v>
+        <v>0.06171539651979921</v>
       </c>
       <c r="W52">
-        <v>0.220956459690644</v>
+        <v>0.2212475095006314</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3055810895640543</v>
+        <v>0.2995893034941709</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1539611987953855</v>
+        <v>0.1558611987953855</v>
       </c>
       <c r="C53">
-        <v>-84.11075263443942</v>
+        <v>-87.3729494785978</v>
       </c>
       <c r="D53">
-        <v>43.74624736556058</v>
+        <v>42.9910505214022</v>
       </c>
       <c r="E53">
-        <v>100.957</v>
+        <v>103.464</v>
       </c>
       <c r="F53">
-        <v>127.857</v>
+        <v>130.364</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5621,37 +5621,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M53">
-        <v>30.14868060000001</v>
+        <v>30.7398312</v>
       </c>
       <c r="N53">
-        <v>-21.11645837777778</v>
+        <v>-21.70760897777778</v>
       </c>
       <c r="O53">
-        <v>-4.349990425822224</v>
+        <v>-4.471767449422223</v>
       </c>
       <c r="P53">
-        <v>-16.76646795195556</v>
+        <v>-17.23584152835555</v>
       </c>
       <c r="Q53">
-        <v>-11.57646795195556</v>
+        <v>-12.04584152835555</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.08392850806135405</v>
+        <v>0.08472285197929892</v>
       </c>
       <c r="T53">
-        <v>0.8805660060358904</v>
+        <v>0.898911131161638</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06171539651979921</v>
+        <v>0.06052856197134154</v>
       </c>
       <c r="W53">
-        <v>0.2212475095006314</v>
+        <v>0.2215273650871577</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2995893034941709</v>
+        <v>0.2938279707346676</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1558611987953855</v>
+        <v>0.1577611987953855</v>
       </c>
       <c r="C54">
-        <v>-87.3729494785978</v>
+        <v>-90.60951469288194</v>
       </c>
       <c r="D54">
-        <v>42.9910505214022</v>
+        <v>42.26148530711806</v>
       </c>
       <c r="E54">
-        <v>103.464</v>
+        <v>105.971</v>
       </c>
       <c r="F54">
-        <v>130.364</v>
+        <v>132.871</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5703,37 +5703,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M54">
-        <v>30.7398312</v>
+        <v>31.3309818</v>
       </c>
       <c r="N54">
-        <v>-21.70760897777778</v>
+        <v>-22.29875957777778</v>
       </c>
       <c r="O54">
-        <v>-4.471767449422223</v>
+        <v>-4.593544473022223</v>
       </c>
       <c r="P54">
-        <v>-17.23584152835555</v>
+        <v>-17.70521510475556</v>
       </c>
       <c r="Q54">
-        <v>-12.04584152835555</v>
+        <v>-12.51521510475555</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.08472285197929892</v>
+        <v>0.08555099776609251</v>
       </c>
       <c r="T54">
-        <v>0.898911131161638</v>
+        <v>0.9180368999097579</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06052856197134154</v>
+        <v>0.05938651363225961</v>
       </c>
       <c r="W54">
-        <v>0.2215273650871577</v>
+        <v>0.2217966600855132</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2938279707346676</v>
+        <v>0.2882840467585418</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1577611987953855</v>
+        <v>0.1596611987953855</v>
       </c>
       <c r="C55">
-        <v>-90.60951469288194</v>
+        <v>-93.82173142108294</v>
       </c>
       <c r="D55">
-        <v>42.26148530711806</v>
+        <v>41.55626857891707</v>
       </c>
       <c r="E55">
-        <v>105.971</v>
+        <v>108.478</v>
       </c>
       <c r="F55">
-        <v>132.871</v>
+        <v>135.378</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5785,37 +5785,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M55">
-        <v>31.3309818</v>
+        <v>31.92213240000001</v>
       </c>
       <c r="N55">
-        <v>-22.29875957777778</v>
+        <v>-22.88991017777778</v>
       </c>
       <c r="O55">
-        <v>-4.593544473022223</v>
+        <v>-4.715321496622224</v>
       </c>
       <c r="P55">
-        <v>-17.70521510475556</v>
+        <v>-18.17458868115556</v>
       </c>
       <c r="Q55">
-        <v>-12.51521510475555</v>
+        <v>-12.98458868115556</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.08555099776609251</v>
+        <v>0.08641514989144236</v>
       </c>
       <c r="T55">
-        <v>0.9180368999097579</v>
+        <v>0.9379942238208397</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05938651363225961</v>
+        <v>0.05828676337981036</v>
       </c>
       <c r="W55">
-        <v>0.2217966600855132</v>
+        <v>0.2220559811950407</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2882840467585418</v>
+        <v>0.2829454533000503</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1596611987953855</v>
+        <v>0.1615611987953855</v>
       </c>
       <c r="C56">
-        <v>-93.82173142108294</v>
+        <v>-97.01079856552835</v>
       </c>
       <c r="D56">
-        <v>41.55626857891707</v>
+        <v>40.87420143447167</v>
       </c>
       <c r="E56">
-        <v>108.478</v>
+        <v>110.985</v>
       </c>
       <c r="F56">
-        <v>135.378</v>
+        <v>137.885</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5867,37 +5867,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M56">
-        <v>31.92213240000001</v>
+        <v>32.51328300000001</v>
       </c>
       <c r="N56">
-        <v>-22.88991017777778</v>
+        <v>-23.48106077777778</v>
       </c>
       <c r="O56">
-        <v>-4.715321496622224</v>
+        <v>-4.837098520222224</v>
       </c>
       <c r="P56">
-        <v>-18.17458868115556</v>
+        <v>-18.64396225755556</v>
       </c>
       <c r="Q56">
-        <v>-12.98458868115556</v>
+        <v>-13.45396225755556</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.08641514989144236</v>
+        <v>0.08731770877791886</v>
       </c>
       <c r="T56">
-        <v>0.9379942238208397</v>
+        <v>0.9588385399057474</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05828676337981036</v>
+        <v>0.05722700404563199</v>
       </c>
       <c r="W56">
-        <v>0.2220559811950407</v>
+        <v>0.22230587244604</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2829454533000503</v>
+        <v>0.2778009905127766</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1615611987953855</v>
+        <v>0.1634611987953855</v>
       </c>
       <c r="C57">
-        <v>-97.01079856552835</v>
+        <v>-100.1778375887628</v>
       </c>
       <c r="D57">
-        <v>40.87420143447167</v>
+        <v>40.21416241123726</v>
       </c>
       <c r="E57">
-        <v>110.985</v>
+        <v>113.492</v>
       </c>
       <c r="F57">
-        <v>137.885</v>
+        <v>140.392</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5949,37 +5949,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M57">
-        <v>32.51328300000001</v>
+        <v>33.10443360000001</v>
       </c>
       <c r="N57">
-        <v>-23.48106077777778</v>
+        <v>-24.07221137777778</v>
       </c>
       <c r="O57">
-        <v>-4.837098520222224</v>
+        <v>-4.958875543822224</v>
       </c>
       <c r="P57">
-        <v>-18.64396225755556</v>
+        <v>-19.11333583395556</v>
       </c>
       <c r="Q57">
-        <v>-13.45396225755556</v>
+        <v>-13.92333583395556</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.08731770877791886</v>
+        <v>0.08826129306832609</v>
       </c>
       <c r="T57">
-        <v>0.9588385399057474</v>
+        <v>0.9806303249036051</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05722700404563199</v>
+        <v>0.05620509325910285</v>
       </c>
       <c r="W57">
-        <v>0.22230587244604</v>
+        <v>0.2225468390095036</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2778009905127766</v>
+        <v>0.2728402585393342</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1634611987953855</v>
+        <v>0.1653611987953855</v>
       </c>
       <c r="C58">
-        <v>-100.1778375887628</v>
+        <v>-103.3238986666975</v>
       </c>
       <c r="D58">
-        <v>40.21416241123726</v>
+        <v>39.57510133330252</v>
       </c>
       <c r="E58">
-        <v>113.492</v>
+        <v>115.999</v>
       </c>
       <c r="F58">
-        <v>140.392</v>
+        <v>142.899</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6031,37 +6031,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M58">
-        <v>33.10443360000001</v>
+        <v>33.69558420000001</v>
       </c>
       <c r="N58">
-        <v>-24.07221137777778</v>
+        <v>-24.66336197777778</v>
       </c>
       <c r="O58">
-        <v>-4.958875543822224</v>
+        <v>-5.080652567422224</v>
       </c>
       <c r="P58">
-        <v>-19.11333583395556</v>
+        <v>-19.58270941035556</v>
       </c>
       <c r="Q58">
-        <v>-13.92333583395556</v>
+        <v>-14.39270941035556</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.08826129306832609</v>
+        <v>0.08924876500014764</v>
       </c>
       <c r="T58">
-        <v>0.9806303249036051</v>
+        <v>1.003435681296712</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05620509325910285</v>
+        <v>0.05521903899139929</v>
       </c>
       <c r="W58">
-        <v>0.2225468390095036</v>
+        <v>0.2227793506058281</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.2728402585393342</v>
+        <v>0.2680535873368898</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1653611987953855</v>
+        <v>0.1672611987953855</v>
       </c>
       <c r="C59">
-        <v>-103.3238986666975</v>
+        <v>-106.4499662642432</v>
       </c>
       <c r="D59">
-        <v>39.57510133330252</v>
+        <v>38.95603373575685</v>
       </c>
       <c r="E59">
-        <v>115.999</v>
+        <v>118.506</v>
       </c>
       <c r="F59">
-        <v>142.899</v>
+        <v>145.406</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6113,37 +6113,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M59">
-        <v>33.69558420000001</v>
+        <v>34.28673480000001</v>
       </c>
       <c r="N59">
-        <v>-24.66336197777778</v>
+        <v>-25.25451257777779</v>
       </c>
       <c r="O59">
-        <v>-5.080652567422224</v>
+        <v>-5.202429591022224</v>
       </c>
       <c r="P59">
-        <v>-19.58270941035556</v>
+        <v>-20.05208298675556</v>
       </c>
       <c r="Q59">
-        <v>-14.39270941035556</v>
+        <v>-14.86208298675556</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.08924876500014764</v>
+        <v>0.09028325940491305</v>
       </c>
       <c r="T59">
-        <v>1.003435681296712</v>
+        <v>1.027327007041872</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05521903899139929</v>
+        <v>0.05426698659499585</v>
       </c>
       <c r="W59">
-        <v>0.2227793506058281</v>
+        <v>0.2230038445609</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2680535873368898</v>
+        <v>0.2634319737621157</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1672611987953855</v>
+        <v>0.1691611987953855</v>
       </c>
       <c r="C60">
-        <v>-106.4499662642432</v>
+        <v>-109.5569641956892</v>
       </c>
       <c r="D60">
-        <v>38.95603373575685</v>
+        <v>38.35603580431081</v>
       </c>
       <c r="E60">
-        <v>118.506</v>
+        <v>121.013</v>
       </c>
       <c r="F60">
-        <v>145.406</v>
+        <v>147.913</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6195,37 +6195,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M60">
-        <v>34.2867348</v>
+        <v>34.8778854</v>
       </c>
       <c r="N60">
-        <v>-25.25451257777778</v>
+        <v>-25.84566317777778</v>
       </c>
       <c r="O60">
-        <v>-5.202429591022224</v>
+        <v>-5.324206614622224</v>
       </c>
       <c r="P60">
-        <v>-20.05208298675556</v>
+        <v>-20.52145656315556</v>
       </c>
       <c r="Q60">
-        <v>-14.86208298675556</v>
+        <v>-15.33145656315556</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09028325940491305</v>
+        <v>0.09136821695137434</v>
       </c>
       <c r="T60">
-        <v>1.027327007041872</v>
+        <v>1.052383763311186</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05426698659499586</v>
+        <v>0.05334720716118237</v>
       </c>
       <c r="W60">
-        <v>0.2230038445609</v>
+        <v>0.2232207285513932</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2634319737621158</v>
+        <v>0.2589670250542834</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1691611987953855</v>
+        <v>0.1710611987953855</v>
       </c>
       <c r="C61">
-        <v>-109.5569641956892</v>
+        <v>-112.6457602245396</v>
       </c>
       <c r="D61">
-        <v>38.35603580431081</v>
+        <v>37.77423977546044</v>
       </c>
       <c r="E61">
-        <v>121.013</v>
+        <v>123.52</v>
       </c>
       <c r="F61">
-        <v>147.913</v>
+        <v>150.42</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6277,37 +6277,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M61">
-        <v>34.8778854</v>
+        <v>35.469036</v>
       </c>
       <c r="N61">
-        <v>-25.84566317777778</v>
+        <v>-26.43681377777778</v>
       </c>
       <c r="O61">
-        <v>-5.324206614622224</v>
+        <v>-5.445983638222223</v>
       </c>
       <c r="P61">
-        <v>-20.52145656315556</v>
+        <v>-20.99083013955556</v>
       </c>
       <c r="Q61">
-        <v>-15.33145656315556</v>
+        <v>-15.80083013955555</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.09136821695137434</v>
+        <v>0.0925074223751587</v>
       </c>
       <c r="T61">
-        <v>1.052383763311186</v>
+        <v>1.078693357393966</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05334720716118237</v>
+        <v>0.05245808704182934</v>
       </c>
       <c r="W61">
-        <v>0.2232207285513932</v>
+        <v>0.2234303830755367</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2589670250542834</v>
+        <v>0.2546509079700453</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1710611987953855</v>
+        <v>0.1729611987953855</v>
       </c>
       <c r="C62">
-        <v>-112.6457602245396</v>
+        <v>-115.7171702509727</v>
       </c>
       <c r="D62">
-        <v>37.77423977546044</v>
+        <v>37.20982974902729</v>
       </c>
       <c r="E62">
-        <v>123.52</v>
+        <v>126.027</v>
       </c>
       <c r="F62">
-        <v>150.42</v>
+        <v>152.927</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6359,37 +6359,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M62">
-        <v>35.469036</v>
+        <v>36.06018660000001</v>
       </c>
       <c r="N62">
-        <v>-26.43681377777778</v>
+        <v>-27.02796437777778</v>
       </c>
       <c r="O62">
-        <v>-5.445983638222223</v>
+        <v>-5.567760661822224</v>
       </c>
       <c r="P62">
-        <v>-20.99083013955556</v>
+        <v>-21.46020371595556</v>
       </c>
       <c r="Q62">
-        <v>-15.80083013955555</v>
+        <v>-16.27020371595556</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.0925074223751587</v>
+        <v>0.09370504858990636</v>
       </c>
       <c r="T62">
-        <v>1.078693357393966</v>
+        <v>1.106352161429708</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05245808704182934</v>
+        <v>0.05159811840179934</v>
       </c>
       <c r="W62">
-        <v>0.2234303830755367</v>
+        <v>0.2236331636808557</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2546509079700453</v>
+        <v>0.2504763029213559</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1729611987953855</v>
+        <v>0.1748611987953854</v>
       </c>
       <c r="C63">
-        <v>-115.7171702509727</v>
+        <v>-118.7719621294229</v>
       </c>
       <c r="D63">
-        <v>37.20982974902729</v>
+        <v>36.66203787057714</v>
       </c>
       <c r="E63">
-        <v>126.027</v>
+        <v>128.534</v>
       </c>
       <c r="F63">
-        <v>152.927</v>
+        <v>155.434</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6441,37 +6441,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M63">
-        <v>36.06018660000001</v>
+        <v>36.6513372</v>
       </c>
       <c r="N63">
-        <v>-27.02796437777778</v>
+        <v>-27.61911497777778</v>
       </c>
       <c r="O63">
-        <v>-5.567760661822224</v>
+        <v>-5.689537685422223</v>
       </c>
       <c r="P63">
-        <v>-21.46020371595556</v>
+        <v>-21.92957729235555</v>
       </c>
       <c r="Q63">
-        <v>-16.27020371595556</v>
+        <v>-16.73957729235555</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.09370504858990636</v>
+        <v>0.09496570776332494</v>
       </c>
       <c r="T63">
-        <v>1.106352161429708</v>
+        <v>1.135466691993648</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05159811840179934</v>
+        <v>0.05076589068564129</v>
       </c>
       <c r="W63">
-        <v>0.2236331636808557</v>
+        <v>0.2238294029763258</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2504763029213559</v>
+        <v>0.2464363625516568</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1748611987953854</v>
+        <v>0.1767611987953855</v>
       </c>
       <c r="C64">
-        <v>-118.7719621294229</v>
+        <v>-121.8108591538456</v>
       </c>
       <c r="D64">
-        <v>36.66203787057714</v>
+        <v>36.13014084615444</v>
       </c>
       <c r="E64">
-        <v>128.534</v>
+        <v>131.041</v>
       </c>
       <c r="F64">
-        <v>155.434</v>
+        <v>157.941</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6523,37 +6523,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M64">
-        <v>36.6513372</v>
+        <v>37.2424878</v>
       </c>
       <c r="N64">
-        <v>-27.61911497777778</v>
+        <v>-28.21026557777778</v>
       </c>
       <c r="O64">
-        <v>-5.689537685422223</v>
+        <v>-5.811314709022223</v>
       </c>
       <c r="P64">
-        <v>-21.92957729235555</v>
+        <v>-22.39895086875555</v>
       </c>
       <c r="Q64">
-        <v>-16.73957729235555</v>
+        <v>-17.20895086875555</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.09496570776332494</v>
+        <v>0.09629451067584724</v>
       </c>
       <c r="T64">
-        <v>1.135466691993648</v>
+        <v>1.166154980966449</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05076589068564129</v>
+        <v>0.04996008289698033</v>
       </c>
       <c r="W64">
-        <v>0.2238294029763258</v>
+        <v>0.2240194124528921</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2464363625516568</v>
+        <v>0.242524674257186</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1767611987953855</v>
+        <v>0.1786611987953855</v>
       </c>
       <c r="C65">
-        <v>-121.8108591538456</v>
+        <v>-124.8345432439343</v>
       </c>
       <c r="D65">
-        <v>36.13014084615444</v>
+        <v>35.61345675606567</v>
       </c>
       <c r="E65">
-        <v>131.041</v>
+        <v>133.548</v>
       </c>
       <c r="F65">
-        <v>157.941</v>
+        <v>160.448</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6605,37 +6605,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M65">
-        <v>37.2424878</v>
+        <v>37.83363840000001</v>
       </c>
       <c r="N65">
-        <v>-28.21026557777778</v>
+        <v>-28.80141617777778</v>
       </c>
       <c r="O65">
-        <v>-5.811314709022223</v>
+        <v>-5.933091732622223</v>
       </c>
       <c r="P65">
-        <v>-22.39895086875555</v>
+        <v>-22.86832444515556</v>
       </c>
       <c r="Q65">
-        <v>-17.20895086875555</v>
+        <v>-17.67832444515556</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.09629451067584724</v>
+        <v>0.09769713597239857</v>
       </c>
       <c r="T65">
-        <v>1.166154980966449</v>
+        <v>1.198548174882184</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04996008289698033</v>
+        <v>0.04917945660171499</v>
       </c>
       <c r="W65">
-        <v>0.2240194124528921</v>
+        <v>0.2242034841333156</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.242524674257186</v>
+        <v>0.2387352262219175</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1786611987953855</v>
+        <v>0.1805611987953855</v>
       </c>
       <c r="C66">
-        <v>-124.8345432439343</v>
+        <v>-127.8436578618019</v>
       </c>
       <c r="D66">
-        <v>35.61345675606567</v>
+        <v>35.11134213819808</v>
       </c>
       <c r="E66">
-        <v>133.548</v>
+        <v>136.055</v>
       </c>
       <c r="F66">
-        <v>160.448</v>
+        <v>162.955</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6687,37 +6687,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M66">
-        <v>37.83363840000001</v>
+        <v>38.424789</v>
       </c>
       <c r="N66">
-        <v>-28.80141617777778</v>
+        <v>-29.39256677777778</v>
       </c>
       <c r="O66">
-        <v>-5.933091732622223</v>
+        <v>-6.054868756222223</v>
       </c>
       <c r="P66">
-        <v>-22.86832444515556</v>
+        <v>-23.33769802155556</v>
       </c>
       <c r="Q66">
-        <v>-17.67832444515556</v>
+        <v>-18.14769802155556</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.09769713597239857</v>
+        <v>0.09917991128589568</v>
       </c>
       <c r="T66">
-        <v>1.198548174882184</v>
+        <v>1.232792408450247</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04917945660171499</v>
+        <v>0.04842284957707323</v>
       </c>
       <c r="W66">
-        <v>0.2242034841333156</v>
+        <v>0.2243818920697261</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2387352262219175</v>
+        <v>0.2350623765877341</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1805611987953855</v>
+        <v>0.1824611987953855</v>
       </c>
       <c r="C67">
-        <v>-127.8436578618019</v>
+        <v>-130.8388106853584</v>
       </c>
       <c r="D67">
-        <v>35.11134213819808</v>
+        <v>34.62318931464164</v>
       </c>
       <c r="E67">
-        <v>136.055</v>
+        <v>138.562</v>
       </c>
       <c r="F67">
-        <v>162.955</v>
+        <v>165.462</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6769,37 +6769,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M67">
-        <v>38.424789</v>
+        <v>39.0159396</v>
       </c>
       <c r="N67">
-        <v>-29.39256677777778</v>
+        <v>-29.98371737777778</v>
       </c>
       <c r="O67">
-        <v>-6.054868756222223</v>
+        <v>-6.176645779822223</v>
       </c>
       <c r="P67">
-        <v>-23.33769802155556</v>
+        <v>-23.80707159795556</v>
       </c>
       <c r="Q67">
-        <v>-18.14769802155556</v>
+        <v>-18.61707159795555</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.09917991128589568</v>
+        <v>0.1007499086766573</v>
       </c>
       <c r="T67">
-        <v>1.232792408450247</v>
+        <v>1.269051008698783</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04842284957707323</v>
+        <v>0.04768917003802667</v>
       </c>
       <c r="W67">
-        <v>0.2243818920697261</v>
+        <v>0.2245548937050333</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2350623765877341</v>
+        <v>0.2315008254273139</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1824611987953855</v>
+        <v>0.1843611987953855</v>
       </c>
       <c r="C68">
-        <v>-130.8388106853584</v>
+        <v>-133.8205760617388</v>
       </c>
       <c r="D68">
-        <v>34.62318931464164</v>
+        <v>34.14842393826118</v>
       </c>
       <c r="E68">
-        <v>138.562</v>
+        <v>141.069</v>
       </c>
       <c r="F68">
-        <v>165.462</v>
+        <v>167.969</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6851,37 +6851,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M68">
-        <v>39.0159396</v>
+        <v>39.60709020000001</v>
       </c>
       <c r="N68">
-        <v>-29.98371737777778</v>
+        <v>-30.57486797777779</v>
       </c>
       <c r="O68">
-        <v>-6.176645779822223</v>
+        <v>-6.298422803422224</v>
       </c>
       <c r="P68">
-        <v>-23.80707159795556</v>
+        <v>-24.27644517435556</v>
       </c>
       <c r="Q68">
-        <v>-18.61707159795555</v>
+        <v>-19.08644517435556</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1007499086766573</v>
+        <v>0.1024150574244348</v>
       </c>
       <c r="T68">
-        <v>1.269051008698783</v>
+        <v>1.307507099871474</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.04768917003802667</v>
+        <v>0.04697739138074267</v>
       </c>
       <c r="W68">
-        <v>0.2245548937050333</v>
+        <v>0.2247227311124209</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2315008254273139</v>
+        <v>0.2280455892269062</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1843611987953855</v>
+        <v>0.1862611987953855</v>
       </c>
       <c r="C69">
-        <v>-133.8205760617388</v>
+        <v>-136.7894972616085</v>
       </c>
       <c r="D69">
-        <v>34.14842393826118</v>
+        <v>33.68650273839152</v>
       </c>
       <c r="E69">
-        <v>141.069</v>
+        <v>143.576</v>
       </c>
       <c r="F69">
-        <v>167.969</v>
+        <v>170.476</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6933,37 +6933,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M69">
-        <v>39.60709020000001</v>
+        <v>40.19824080000001</v>
       </c>
       <c r="N69">
-        <v>-30.57486797777779</v>
+        <v>-31.16601857777778</v>
       </c>
       <c r="O69">
-        <v>-6.298422803422224</v>
+        <v>-6.420199827022224</v>
       </c>
       <c r="P69">
-        <v>-24.27644517435556</v>
+        <v>-24.74581875075556</v>
       </c>
       <c r="Q69">
-        <v>-19.08644517435556</v>
+        <v>-19.55581875075556</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1024150574244348</v>
+        <v>0.1041842779689484</v>
       </c>
       <c r="T69">
-        <v>1.307507099871474</v>
+        <v>1.348366696742457</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.04697739138074267</v>
+        <v>0.04628654738984941</v>
       </c>
       <c r="W69">
-        <v>0.2247227311124209</v>
+        <v>0.2248856321254735</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2280455892269062</v>
+        <v>0.2246919776206282</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1862611987953855</v>
+        <v>0.1881611987953855</v>
       </c>
       <c r="C70">
-        <v>-136.7894972616085</v>
+        <v>-139.7460885529472</v>
       </c>
       <c r="D70">
-        <v>33.68650273839152</v>
+        <v>33.23691144705281</v>
       </c>
       <c r="E70">
-        <v>143.576</v>
+        <v>146.083</v>
       </c>
       <c r="F70">
-        <v>170.476</v>
+        <v>172.983</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -7015,37 +7015,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M70">
-        <v>40.19824080000001</v>
+        <v>40.78939140000001</v>
       </c>
       <c r="N70">
-        <v>-31.16601857777778</v>
+        <v>-31.75716917777778</v>
       </c>
       <c r="O70">
-        <v>-6.420199827022224</v>
+        <v>-6.541976850622224</v>
       </c>
       <c r="P70">
-        <v>-24.74581875075556</v>
+        <v>-25.21519232715556</v>
       </c>
       <c r="Q70">
-        <v>-19.55581875075556</v>
+        <v>-20.02519232715556</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1041842779689484</v>
+        <v>0.1060676417743983</v>
       </c>
       <c r="T70">
-        <v>1.348366696742457</v>
+        <v>1.391862396637375</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04628654738984941</v>
+        <v>0.04561572786246029</v>
       </c>
       <c r="W70">
-        <v>0.2248856321254735</v>
+        <v>0.2250438113700319</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2246919776206282</v>
+        <v>0.2214355721478655</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1881611987953855</v>
+        <v>0.1900611987953855</v>
       </c>
       <c r="C71">
-        <v>-139.7460885529472</v>
+        <v>-142.6908371109567</v>
       </c>
       <c r="D71">
-        <v>33.23691144705281</v>
+        <v>32.7991628890433</v>
       </c>
       <c r="E71">
-        <v>146.083</v>
+        <v>148.59</v>
       </c>
       <c r="F71">
-        <v>172.983</v>
+        <v>175.49</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7097,37 +7097,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M71">
-        <v>40.78939140000001</v>
+        <v>41.38054200000001</v>
       </c>
       <c r="N71">
-        <v>-31.75716917777778</v>
+        <v>-32.34831977777779</v>
       </c>
       <c r="O71">
-        <v>-6.541976850622224</v>
+        <v>-6.663753874222225</v>
       </c>
       <c r="P71">
-        <v>-25.21519232715556</v>
+        <v>-25.68456590355557</v>
       </c>
       <c r="Q71">
-        <v>-20.02519232715556</v>
+        <v>-20.49456590355556</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1060676417743983</v>
+        <v>0.1080765631668783</v>
       </c>
       <c r="T71">
-        <v>1.391862396637375</v>
+        <v>1.438257809858621</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04561572786246029</v>
+        <v>0.04496407460728227</v>
       </c>
       <c r="W71">
-        <v>0.2250438113700319</v>
+        <v>0.2251974712076029</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2214355721478655</v>
+        <v>0.2182722068314673</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1900611987953855</v>
+        <v>0.1919611987953855</v>
       </c>
       <c r="C72">
-        <v>-142.6908371109567</v>
+        <v>-145.6242047790026</v>
       </c>
       <c r="D72">
-        <v>32.7991628890433</v>
+        <v>32.37279522099739</v>
       </c>
       <c r="E72">
-        <v>148.59</v>
+        <v>151.097</v>
       </c>
       <c r="F72">
-        <v>175.49</v>
+        <v>177.997</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7179,37 +7179,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M72">
-        <v>41.38054200000001</v>
+        <v>41.97169260000001</v>
       </c>
       <c r="N72">
-        <v>-32.34831977777779</v>
+        <v>-32.93947037777779</v>
       </c>
       <c r="O72">
-        <v>-6.663753874222225</v>
+        <v>-6.785530897822225</v>
       </c>
       <c r="P72">
-        <v>-25.68456590355557</v>
+        <v>-26.15393947995556</v>
       </c>
       <c r="Q72">
-        <v>-20.49456590355556</v>
+        <v>-20.96393947995556</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1080765631668783</v>
+        <v>0.1102240308622879</v>
       </c>
       <c r="T72">
-        <v>1.438257809858621</v>
+        <v>1.487852906750298</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04496407460728227</v>
+        <v>0.04433077778182759</v>
       </c>
       <c r="W72">
-        <v>0.2251974712076029</v>
+        <v>0.2253468025990451</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2182722068314673</v>
+        <v>0.2151979503972213</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1919611987953855</v>
+        <v>0.1938611987953855</v>
       </c>
       <c r="C73">
-        <v>-145.6242047790026</v>
+        <v>-148.5466296939724</v>
       </c>
       <c r="D73">
-        <v>32.37279522099742</v>
+        <v>31.95737030602764</v>
       </c>
       <c r="E73">
-        <v>151.097</v>
+        <v>153.604</v>
       </c>
       <c r="F73">
-        <v>177.997</v>
+        <v>180.504</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7261,37 +7261,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M73">
-        <v>41.9716926</v>
+        <v>42.5628432</v>
       </c>
       <c r="N73">
-        <v>-32.93947037777778</v>
+        <v>-33.53062097777778</v>
       </c>
       <c r="O73">
-        <v>-6.785530897822223</v>
+        <v>-6.907307921422223</v>
       </c>
       <c r="P73">
-        <v>-26.15393947995556</v>
+        <v>-26.62331305635556</v>
       </c>
       <c r="Q73">
-        <v>-20.96393947995556</v>
+        <v>-21.43331305635555</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1102240308622879</v>
+        <v>0.1125248891073696</v>
       </c>
       <c r="T73">
-        <v>1.487852906750297</v>
+        <v>1.540990510562808</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0443307777818276</v>
+        <v>0.04371507253485778</v>
       </c>
       <c r="W73">
-        <v>0.2253468025990451</v>
+        <v>0.2254919858962806</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2151979503972213</v>
+        <v>0.2122090899750377</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1938611987953855</v>
+        <v>0.1957611987953855</v>
       </c>
       <c r="C74">
-        <v>-148.5466296939724</v>
+        <v>-151.458527788074</v>
       </c>
       <c r="D74">
-        <v>31.95737030602764</v>
+        <v>31.55247221192597</v>
       </c>
       <c r="E74">
-        <v>153.604</v>
+        <v>156.111</v>
       </c>
       <c r="F74">
-        <v>180.504</v>
+        <v>183.011</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7343,37 +7343,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M74">
-        <v>42.5628432</v>
+        <v>43.1539938</v>
       </c>
       <c r="N74">
-        <v>-33.53062097777778</v>
+        <v>-34.12177157777778</v>
       </c>
       <c r="O74">
-        <v>-6.907307921422223</v>
+        <v>-7.029084945022223</v>
       </c>
       <c r="P74">
-        <v>-26.62331305635556</v>
+        <v>-27.09268663275556</v>
       </c>
       <c r="Q74">
-        <v>-21.43331305635555</v>
+        <v>-21.90268663275555</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1125248891073696</v>
+        <v>0.1149961812965314</v>
       </c>
       <c r="T74">
-        <v>1.540990510562808</v>
+        <v>1.598064233176245</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04371507253485778</v>
+        <v>0.04311623592479123</v>
       </c>
       <c r="W74">
-        <v>0.2254919858962806</v>
+        <v>0.2256331915689342</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2122090899750377</v>
+        <v>0.2093021161397632</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1957611987953855</v>
+        <v>0.1976611987953855</v>
       </c>
       <c r="C75">
-        <v>-151.458527788074</v>
+        <v>-154.3602941778971</v>
       </c>
       <c r="D75">
-        <v>31.55247221192597</v>
+        <v>31.1577058221029</v>
       </c>
       <c r="E75">
-        <v>156.111</v>
+        <v>158.618</v>
       </c>
       <c r="F75">
-        <v>183.011</v>
+        <v>185.518</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7425,37 +7425,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M75">
-        <v>43.1539938</v>
+        <v>43.7451444</v>
       </c>
       <c r="N75">
-        <v>-34.12177157777778</v>
+        <v>-34.71292217777778</v>
       </c>
       <c r="O75">
-        <v>-7.029084945022223</v>
+        <v>-7.150861968622222</v>
       </c>
       <c r="P75">
-        <v>-27.09268663275556</v>
+        <v>-27.56206020915555</v>
       </c>
       <c r="Q75">
-        <v>-21.90268663275555</v>
+        <v>-22.37206020915555</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1149961812965314</v>
+        <v>0.1176575728848595</v>
       </c>
       <c r="T75">
-        <v>1.598064233176245</v>
+        <v>1.659528242144562</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04311623592479123</v>
+        <v>0.04253358408796973</v>
       </c>
       <c r="W75">
-        <v>0.2256331915689342</v>
+        <v>0.2257705808720568</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2093021161397632</v>
+        <v>0.2064737091649016</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1976611987953855</v>
+        <v>0.1995611987953854</v>
       </c>
       <c r="C76">
-        <v>-154.3602941778971</v>
+        <v>-157.2523044504872</v>
       </c>
       <c r="D76">
-        <v>31.1577058221029</v>
+        <v>30.77269554951279</v>
       </c>
       <c r="E76">
-        <v>158.618</v>
+        <v>161.125</v>
       </c>
       <c r="F76">
-        <v>185.518</v>
+        <v>188.025</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7507,37 +7507,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M76">
-        <v>43.7451444</v>
+        <v>44.336295</v>
       </c>
       <c r="N76">
-        <v>-34.71292217777778</v>
+        <v>-35.30407277777778</v>
       </c>
       <c r="O76">
-        <v>-7.150861968622222</v>
+        <v>-7.272638992222222</v>
       </c>
       <c r="P76">
-        <v>-27.56206020915555</v>
+        <v>-28.03143378555555</v>
       </c>
       <c r="Q76">
-        <v>-22.37206020915555</v>
+        <v>-22.84143378555555</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1176575728848595</v>
+        <v>0.1205318758002539</v>
       </c>
       <c r="T76">
-        <v>1.659528242144562</v>
+        <v>1.725909371830345</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04253358408796973</v>
+        <v>0.04196646963346347</v>
       </c>
       <c r="W76">
-        <v>0.2257705808720568</v>
+        <v>0.2259043064604293</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2064737091649016</v>
+        <v>0.2037207263760362</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1995611987953854</v>
+        <v>0.2014611987953855</v>
       </c>
       <c r="C77">
-        <v>-157.2523044504872</v>
+        <v>-160.1349158552338</v>
       </c>
       <c r="D77">
-        <v>30.77269554951279</v>
+        <v>30.39708414476617</v>
       </c>
       <c r="E77">
-        <v>161.125</v>
+        <v>163.632</v>
       </c>
       <c r="F77">
-        <v>188.025</v>
+        <v>190.532</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7589,37 +7589,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M77">
-        <v>44.336295</v>
+        <v>44.92744560000001</v>
       </c>
       <c r="N77">
-        <v>-35.30407277777778</v>
+        <v>-35.89522337777778</v>
       </c>
       <c r="O77">
-        <v>-7.272638992222222</v>
+        <v>-7.394416015822224</v>
       </c>
       <c r="P77">
-        <v>-28.03143378555555</v>
+        <v>-28.50080736195556</v>
       </c>
       <c r="Q77">
-        <v>-22.84143378555555</v>
+        <v>-23.31080736195556</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1205318758002539</v>
+        <v>0.1236457039585978</v>
       </c>
       <c r="T77">
-        <v>1.725909371830345</v>
+        <v>1.797822262323276</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04196646963346347</v>
+        <v>0.04141427924354947</v>
       </c>
       <c r="W77">
-        <v>0.2259043064604293</v>
+        <v>0.226034512954371</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2037207263760362</v>
+        <v>0.2010401905026673</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2014611987953855</v>
+        <v>0.2033611987953855</v>
       </c>
       <c r="C78">
-        <v>-160.1349158552338</v>
+        <v>-163.0084684095214</v>
       </c>
       <c r="D78">
-        <v>30.39708414476617</v>
+        <v>30.03053159047864</v>
       </c>
       <c r="E78">
-        <v>163.632</v>
+        <v>166.139</v>
       </c>
       <c r="F78">
-        <v>190.532</v>
+        <v>193.039</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7671,37 +7671,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M78">
-        <v>44.92744560000001</v>
+        <v>45.5185962</v>
       </c>
       <c r="N78">
-        <v>-35.89522337777778</v>
+        <v>-36.48637397777778</v>
       </c>
       <c r="O78">
-        <v>-7.394416015822224</v>
+        <v>-7.516193039422223</v>
       </c>
       <c r="P78">
-        <v>-28.50080736195556</v>
+        <v>-28.97018093835556</v>
       </c>
       <c r="Q78">
-        <v>-23.31080736195556</v>
+        <v>-23.78018093835556</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1236457039585978</v>
+        <v>0.1270302997828847</v>
       </c>
       <c r="T78">
-        <v>1.797822262323276</v>
+        <v>1.875988447641679</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04141427924354947</v>
+        <v>0.04087643146116571</v>
       </c>
       <c r="W78">
-        <v>0.226034512954371</v>
+        <v>0.2261613374614571</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2010401905026673</v>
+        <v>0.1984292789376976</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2033611987953855</v>
+        <v>0.2052611987953855</v>
       </c>
       <c r="C79">
-        <v>-163.0084684095214</v>
+        <v>-165.8732859253368</v>
       </c>
       <c r="D79">
-        <v>30.03053159047864</v>
+        <v>29.67271407466323</v>
       </c>
       <c r="E79">
-        <v>166.139</v>
+        <v>168.646</v>
       </c>
       <c r="F79">
-        <v>193.039</v>
+        <v>195.546</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7753,37 +7753,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M79">
-        <v>45.5185962</v>
+        <v>46.1097468</v>
       </c>
       <c r="N79">
-        <v>-36.48637397777778</v>
+        <v>-37.07752457777778</v>
       </c>
       <c r="O79">
-        <v>-7.516193039422223</v>
+        <v>-7.637970063022223</v>
       </c>
       <c r="P79">
-        <v>-28.97018093835556</v>
+        <v>-29.43955451475556</v>
       </c>
       <c r="Q79">
-        <v>-23.78018093835556</v>
+        <v>-24.24955451475556</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1270302997828847</v>
+        <v>0.1307225861366522</v>
       </c>
       <c r="T79">
-        <v>1.875988447641679</v>
+        <v>1.96126064980721</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04087643146116571</v>
+        <v>0.04035237464756102</v>
       </c>
       <c r="W79">
-        <v>0.2261613374614571</v>
+        <v>0.2262849100581051</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1984292789376976</v>
+        <v>0.1958853138231118</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2052611987953855</v>
+        <v>0.2071611987953855</v>
       </c>
       <c r="C80">
-        <v>-165.8732859253368</v>
+        <v>-168.7296769633481</v>
       </c>
       <c r="D80">
-        <v>29.67271407466323</v>
+        <v>29.32332303665197</v>
       </c>
       <c r="E80">
-        <v>168.646</v>
+        <v>171.153</v>
       </c>
       <c r="F80">
-        <v>195.546</v>
+        <v>198.053</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7835,37 +7835,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M80">
-        <v>46.1097468</v>
+        <v>46.70089740000001</v>
       </c>
       <c r="N80">
-        <v>-37.07752457777778</v>
+        <v>-37.66867517777779</v>
       </c>
       <c r="O80">
-        <v>-7.637970063022223</v>
+        <v>-7.759747086622225</v>
       </c>
       <c r="P80">
-        <v>-29.43955451475556</v>
+        <v>-29.90892809115556</v>
       </c>
       <c r="Q80">
-        <v>-24.24955451475556</v>
+        <v>-24.71892809115556</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1307225861366522</v>
+        <v>0.1347665188098261</v>
       </c>
       <c r="T80">
-        <v>1.96126064980721</v>
+        <v>2.054654014083744</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04035237464756102</v>
+        <v>0.03984158509506024</v>
       </c>
       <c r="W80">
-        <v>0.2262849100581051</v>
+        <v>0.2264053542345848</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1958853138231118</v>
+        <v>0.1934057528886419</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2071611987953855</v>
+        <v>0.2090611987953855</v>
       </c>
       <c r="C81">
-        <v>-168.7296769633481</v>
+        <v>-171.5779357203627</v>
       </c>
       <c r="D81">
-        <v>29.32332303665197</v>
+        <v>28.98206427963731</v>
       </c>
       <c r="E81">
-        <v>171.153</v>
+        <v>173.66</v>
       </c>
       <c r="F81">
-        <v>198.053</v>
+        <v>200.56</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7917,37 +7917,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M81">
-        <v>46.70089740000001</v>
+        <v>47.29204800000001</v>
       </c>
       <c r="N81">
-        <v>-37.66867517777779</v>
+        <v>-38.25982577777778</v>
       </c>
       <c r="O81">
-        <v>-7.759747086622225</v>
+        <v>-7.881524110222224</v>
       </c>
       <c r="P81">
-        <v>-29.90892809115556</v>
+        <v>-30.37830166755556</v>
       </c>
       <c r="Q81">
-        <v>-24.71892809115556</v>
+        <v>-25.18830166755556</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1347665188098261</v>
+        <v>0.1392148447503174</v>
       </c>
       <c r="T81">
-        <v>2.054654014083744</v>
+        <v>2.157386714787932</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03984158509506024</v>
+        <v>0.039343565281372</v>
       </c>
       <c r="W81">
-        <v>0.2264053542345848</v>
+        <v>0.2265227873066525</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1934057528886419</v>
+        <v>0.1909881809775339</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2090611987953855</v>
+        <v>0.2109611987953855</v>
       </c>
       <c r="C82">
-        <v>-171.5779357203627</v>
+        <v>-174.4183428555309</v>
       </c>
       <c r="D82">
-        <v>28.98206427963731</v>
+        <v>28.64865714446914</v>
       </c>
       <c r="E82">
-        <v>173.66</v>
+        <v>176.167</v>
       </c>
       <c r="F82">
-        <v>200.56</v>
+        <v>203.067</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -7999,37 +7999,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M82">
-        <v>47.29204800000001</v>
+        <v>47.88319860000001</v>
       </c>
       <c r="N82">
-        <v>-38.25982577777778</v>
+        <v>-38.85097637777778</v>
       </c>
       <c r="O82">
-        <v>-7.881524110222224</v>
+        <v>-8.003301133822225</v>
       </c>
       <c r="P82">
-        <v>-30.37830166755556</v>
+        <v>-30.84767524395556</v>
       </c>
       <c r="Q82">
-        <v>-25.18830166755556</v>
+        <v>-25.65767524395556</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1392148447503174</v>
+        <v>0.1441314155266499</v>
       </c>
       <c r="T82">
-        <v>2.157386714787932</v>
+        <v>2.270933383987296</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.039343565281372</v>
+        <v>0.03885784225320691</v>
       </c>
       <c r="W82">
-        <v>0.2265227873066525</v>
+        <v>0.2266373207966938</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1909881809775339</v>
+        <v>0.1886303022000335</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2109611987953855</v>
+        <v>0.2128611987953855</v>
       </c>
       <c r="C83">
-        <v>-174.4183428555309</v>
+        <v>-177.2511662601694</v>
       </c>
       <c r="D83">
-        <v>28.64865714446914</v>
+        <v>28.32283373983069</v>
       </c>
       <c r="E83">
-        <v>176.167</v>
+        <v>178.674</v>
       </c>
       <c r="F83">
-        <v>203.067</v>
+        <v>205.574</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8081,37 +8081,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M83">
-        <v>47.88319860000001</v>
+        <v>48.47434920000001</v>
       </c>
       <c r="N83">
-        <v>-38.85097637777778</v>
+        <v>-39.44212697777779</v>
       </c>
       <c r="O83">
-        <v>-8.003301133822225</v>
+        <v>-8.125078157422225</v>
       </c>
       <c r="P83">
-        <v>-30.84767524395556</v>
+        <v>-31.31704882035557</v>
       </c>
       <c r="Q83">
-        <v>-25.65767524395556</v>
+        <v>-26.12704882035557</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1441314155266499</v>
+        <v>0.1495942719447972</v>
       </c>
       <c r="T83">
-        <v>2.270933383987296</v>
+        <v>2.397096349764369</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03885784225320691</v>
+        <v>0.03838396612816779</v>
       </c>
       <c r="W83">
-        <v>0.2266373207966938</v>
+        <v>0.2267490607869781</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1886303022000335</v>
+        <v>0.1863299326610087</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2128611987953855</v>
+        <v>0.2147611987953855</v>
       </c>
       <c r="C84">
-        <v>-177.2511662601694</v>
+        <v>-180.0766617756448</v>
       </c>
       <c r="D84">
-        <v>28.32283373983069</v>
+        <v>28.00433822435529</v>
       </c>
       <c r="E84">
-        <v>178.674</v>
+        <v>181.181</v>
       </c>
       <c r="F84">
-        <v>205.574</v>
+        <v>208.081</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8163,37 +8163,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M84">
-        <v>48.47434920000001</v>
+        <v>49.06549980000001</v>
       </c>
       <c r="N84">
-        <v>-39.44212697777779</v>
+        <v>-40.03327757777779</v>
       </c>
       <c r="O84">
-        <v>-8.125078157422225</v>
+        <v>-8.246855181022225</v>
       </c>
       <c r="P84">
-        <v>-31.31704882035557</v>
+        <v>-31.78642239675556</v>
       </c>
       <c r="Q84">
-        <v>-26.12704882035557</v>
+        <v>-26.59642239675556</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1495942719447972</v>
+        <v>0.1556998173533146</v>
       </c>
       <c r="T84">
-        <v>2.397096349764369</v>
+        <v>2.538102017397567</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03838396612816779</v>
+        <v>0.03792150870493686</v>
       </c>
       <c r="W84">
-        <v>0.2267490607869781</v>
+        <v>0.2268581082473759</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1863299326610087</v>
+        <v>0.1840849937132857</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2147611987953855</v>
+        <v>0.2166611987953855</v>
       </c>
       <c r="C85">
-        <v>-180.0766617756448</v>
+        <v>-182.8950738633592</v>
       </c>
       <c r="D85">
-        <v>28.00433822435529</v>
+        <v>27.69292613664079</v>
       </c>
       <c r="E85">
-        <v>181.181</v>
+        <v>183.688</v>
       </c>
       <c r="F85">
-        <v>208.081</v>
+        <v>210.588</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8245,37 +8245,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M85">
-        <v>49.06549980000001</v>
+        <v>49.6566504</v>
       </c>
       <c r="N85">
-        <v>-40.03327757777779</v>
+        <v>-40.62442817777778</v>
       </c>
       <c r="O85">
-        <v>-8.246855181022225</v>
+        <v>-8.368632204622223</v>
       </c>
       <c r="P85">
-        <v>-31.78642239675556</v>
+        <v>-32.25579597315556</v>
       </c>
       <c r="Q85">
-        <v>-26.59642239675556</v>
+        <v>-27.06579597315556</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1556998173533146</v>
+        <v>0.1625685559378968</v>
       </c>
       <c r="T85">
-        <v>2.538102017397567</v>
+        <v>2.696733393484916</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03792150870493686</v>
+        <v>0.03747006217273523</v>
       </c>
       <c r="W85">
-        <v>0.2268581082473759</v>
+        <v>0.2269645593396691</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1840849937132857</v>
+        <v>0.1818935056928895</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2166611987953855</v>
+        <v>0.2185611987953855</v>
       </c>
       <c r="C86">
-        <v>-182.8950738633592</v>
+        <v>-185.7066362305256</v>
       </c>
       <c r="D86">
-        <v>27.69292613664079</v>
+        <v>27.38836376947444</v>
       </c>
       <c r="E86">
-        <v>183.688</v>
+        <v>186.195</v>
       </c>
       <c r="F86">
-        <v>210.588</v>
+        <v>213.095</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8327,37 +8327,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M86">
-        <v>49.6566504</v>
+        <v>50.247801</v>
       </c>
       <c r="N86">
-        <v>-40.62442817777778</v>
+        <v>-41.21557877777778</v>
       </c>
       <c r="O86">
-        <v>-8.368632204622223</v>
+        <v>-8.490409228222223</v>
       </c>
       <c r="P86">
-        <v>-32.25579597315556</v>
+        <v>-32.72516954955556</v>
       </c>
       <c r="Q86">
-        <v>-27.06579597315556</v>
+        <v>-27.53516954955556</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1625685559378967</v>
+        <v>0.1703531263337565</v>
       </c>
       <c r="T86">
-        <v>2.696733393484914</v>
+        <v>2.876515619717242</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03747006217273523</v>
+        <v>0.03702923791187953</v>
       </c>
       <c r="W86">
-        <v>0.2269645593396691</v>
+        <v>0.2270685057003788</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1818935056928895</v>
+        <v>0.1797535820965026</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2185611987953855</v>
+        <v>0.2204611987953855</v>
       </c>
       <c r="C87">
-        <v>-185.7066362305256</v>
+        <v>-188.5115724150983</v>
       </c>
       <c r="D87">
-        <v>27.38836376947444</v>
+        <v>27.09042758490168</v>
       </c>
       <c r="E87">
-        <v>186.195</v>
+        <v>188.702</v>
       </c>
       <c r="F87">
-        <v>213.095</v>
+        <v>215.602</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8409,37 +8409,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M87">
-        <v>50.247801</v>
+        <v>50.8389516</v>
       </c>
       <c r="N87">
-        <v>-41.21557877777778</v>
+        <v>-41.80672937777778</v>
       </c>
       <c r="O87">
-        <v>-8.490409228222223</v>
+        <v>-8.612186251822223</v>
       </c>
       <c r="P87">
-        <v>-32.72516954955556</v>
+        <v>-33.19454312595555</v>
       </c>
       <c r="Q87">
-        <v>-27.53516954955556</v>
+        <v>-28.00454312595555</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1703531263337565</v>
+        <v>0.1792497782147391</v>
       </c>
       <c r="T87">
-        <v>2.876515619717242</v>
+        <v>3.081981021125616</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03702923791187953</v>
+        <v>0.03659866537802046</v>
       </c>
       <c r="W87">
-        <v>0.2270685057003788</v>
+        <v>0.2271700347038628</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1797535820965026</v>
+        <v>0.1776634241651479</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2204611987953855</v>
+        <v>0.2223611987953855</v>
       </c>
       <c r="C88">
-        <v>-188.5115724150983</v>
+        <v>-191.3100963329381</v>
       </c>
       <c r="D88">
-        <v>27.09042758490168</v>
+        <v>26.79890366706192</v>
       </c>
       <c r="E88">
-        <v>188.702</v>
+        <v>191.209</v>
       </c>
       <c r="F88">
-        <v>215.602</v>
+        <v>218.109</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8491,37 +8491,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M88">
-        <v>50.8389516</v>
+        <v>51.43010220000001</v>
       </c>
       <c r="N88">
-        <v>-41.80672937777778</v>
+        <v>-42.39787997777778</v>
       </c>
       <c r="O88">
-        <v>-8.612186251822223</v>
+        <v>-8.733963275422225</v>
       </c>
       <c r="P88">
-        <v>-33.19454312595555</v>
+        <v>-33.66391670235556</v>
       </c>
       <c r="Q88">
-        <v>-28.00454312595555</v>
+        <v>-28.47391670235556</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1792497782147391</v>
+        <v>0.1895151457697191</v>
       </c>
       <c r="T88">
-        <v>3.081981021125616</v>
+        <v>3.319056484289125</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03659866537802046</v>
+        <v>0.03617799106333057</v>
       </c>
       <c r="W88">
-        <v>0.2271700347038628</v>
+        <v>0.2272692297072667</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1776634241651479</v>
+        <v>0.1756213158414105</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2223611987953855</v>
+        <v>0.2242611987953855</v>
       </c>
       <c r="C89">
-        <v>-191.3100963329381</v>
+        <v>-194.102412790023</v>
       </c>
       <c r="D89">
-        <v>26.79890366706192</v>
+        <v>26.51358720997706</v>
       </c>
       <c r="E89">
-        <v>191.209</v>
+        <v>193.716</v>
       </c>
       <c r="F89">
-        <v>218.109</v>
+        <v>220.616</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8573,37 +8573,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M89">
-        <v>51.43010220000001</v>
+        <v>52.02125280000001</v>
       </c>
       <c r="N89">
-        <v>-42.39787997777778</v>
+        <v>-42.98903057777778</v>
       </c>
       <c r="O89">
-        <v>-8.733963275422225</v>
+        <v>-8.855740299022225</v>
       </c>
       <c r="P89">
-        <v>-33.66391670235556</v>
+        <v>-34.13329027875556</v>
       </c>
       <c r="Q89">
-        <v>-28.47391670235556</v>
+        <v>-28.94329027875556</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.1895151457697191</v>
+        <v>0.2014914079171957</v>
       </c>
       <c r="T89">
-        <v>3.319056484289125</v>
+        <v>3.595644524646552</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03617799106333057</v>
+        <v>0.03576687752851999</v>
       </c>
       <c r="W89">
-        <v>0.2272692297072667</v>
+        <v>0.227366170278775</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1756213158414105</v>
+        <v>0.1736256190704855</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2242611987953855</v>
+        <v>0.2261611987953855</v>
       </c>
       <c r="C90">
-        <v>-194.102412790023</v>
+        <v>-196.8887179622851</v>
       </c>
       <c r="D90">
-        <v>26.51358720997706</v>
+        <v>26.23428203771489</v>
       </c>
       <c r="E90">
-        <v>193.716</v>
+        <v>196.223</v>
       </c>
       <c r="F90">
-        <v>220.616</v>
+        <v>223.123</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8655,37 +8655,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M90">
-        <v>52.02125280000001</v>
+        <v>52.61240340000001</v>
       </c>
       <c r="N90">
-        <v>-42.98903057777778</v>
+        <v>-43.58018117777778</v>
       </c>
       <c r="O90">
-        <v>-8.855740299022225</v>
+        <v>-8.977517322622223</v>
       </c>
       <c r="P90">
-        <v>-34.13329027875556</v>
+        <v>-34.60266385515555</v>
       </c>
       <c r="Q90">
-        <v>-28.94329027875556</v>
+        <v>-29.41266385515555</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2014914079171957</v>
+        <v>0.2156451722733044</v>
       </c>
       <c r="T90">
-        <v>3.595644524646552</v>
+        <v>3.922521299614421</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03576687752851999</v>
+        <v>0.03536500250010966</v>
       </c>
       <c r="W90">
-        <v>0.227366170278775</v>
+        <v>0.2274609324104742</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1736256190704855</v>
+        <v>0.1716747694180081</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2261611987953855</v>
+        <v>0.2280611987953855</v>
       </c>
       <c r="C91">
-        <v>-196.8887179622851</v>
+        <v>-199.6691998454347</v>
       </c>
       <c r="D91">
-        <v>26.23428203771489</v>
+        <v>25.96080015456533</v>
       </c>
       <c r="E91">
-        <v>196.223</v>
+        <v>198.73</v>
       </c>
       <c r="F91">
-        <v>223.123</v>
+        <v>225.63</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8737,37 +8737,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M91">
-        <v>52.61240340000001</v>
+        <v>53.20355400000001</v>
       </c>
       <c r="N91">
-        <v>-43.58018117777778</v>
+        <v>-44.17133177777779</v>
       </c>
       <c r="O91">
-        <v>-8.977517322622223</v>
+        <v>-9.099294346222225</v>
       </c>
       <c r="P91">
-        <v>-34.60266385515555</v>
+        <v>-35.07203743155556</v>
       </c>
       <c r="Q91">
-        <v>-29.41266385515555</v>
+        <v>-29.88203743155556</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2156451722733044</v>
+        <v>0.2326296895006349</v>
       </c>
       <c r="T91">
-        <v>3.922521299614421</v>
+        <v>4.314773429575864</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03536500250010966</v>
+        <v>0.03497205802788621</v>
       </c>
       <c r="W91">
-        <v>0.2274609324104742</v>
+        <v>0.2275535887170244</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1716747694180081</v>
+        <v>0.1697672719800302</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2280611987953855</v>
+        <v>0.2299611987953855</v>
       </c>
       <c r="C92">
-        <v>-199.6691998454347</v>
+        <v>-202.4440386769384</v>
       </c>
       <c r="D92">
-        <v>25.96080015456533</v>
+        <v>25.69296132306166</v>
       </c>
       <c r="E92">
-        <v>198.73</v>
+        <v>201.237</v>
       </c>
       <c r="F92">
-        <v>225.63</v>
+        <v>228.137</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8819,37 +8819,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M92">
-        <v>53.20355400000001</v>
+        <v>53.79470460000001</v>
       </c>
       <c r="N92">
-        <v>-44.17133177777779</v>
+        <v>-44.76248237777779</v>
       </c>
       <c r="O92">
-        <v>-9.099294346222225</v>
+        <v>-9.221071369822225</v>
       </c>
       <c r="P92">
-        <v>-35.07203743155556</v>
+        <v>-35.54141100795556</v>
       </c>
       <c r="Q92">
-        <v>-29.88203743155556</v>
+        <v>-30.35141100795556</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2326296895006349</v>
+        <v>0.2533885438895943</v>
       </c>
       <c r="T92">
-        <v>4.314773429575864</v>
+        <v>4.794192699528737</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03497205802788621</v>
+        <v>0.03458774969790945</v>
       </c>
       <c r="W92">
-        <v>0.2275535887170244</v>
+        <v>0.227644208621233</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1697672719800302</v>
+        <v>0.1679016975626672</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2299611987953855</v>
+        <v>0.2318611987953855</v>
       </c>
       <c r="C93">
-        <v>-202.4440386769384</v>
+        <v>-205.2134073321436</v>
       </c>
       <c r="D93">
-        <v>25.69296132306166</v>
+        <v>25.43059266785642</v>
       </c>
       <c r="E93">
-        <v>201.237</v>
+        <v>203.744</v>
       </c>
       <c r="F93">
-        <v>228.137</v>
+        <v>230.644</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8901,37 +8901,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M93">
-        <v>53.79470460000001</v>
+        <v>54.38585520000001</v>
       </c>
       <c r="N93">
-        <v>-44.76248237777779</v>
+        <v>-45.35363297777779</v>
       </c>
       <c r="O93">
-        <v>-9.221071369822225</v>
+        <v>-9.342848393422225</v>
       </c>
       <c r="P93">
-        <v>-35.54141100795556</v>
+        <v>-36.01078458435556</v>
       </c>
       <c r="Q93">
-        <v>-30.35141100795556</v>
+        <v>-30.82078458435556</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2533885438895943</v>
+        <v>0.2793371118757936</v>
       </c>
       <c r="T93">
-        <v>4.794192699528737</v>
+        <v>5.393466786969832</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03458774969790945</v>
+        <v>0.03421179589684521</v>
       </c>
       <c r="W93">
-        <v>0.227644208621233</v>
+        <v>0.2277328585275239</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1679016975626672</v>
+        <v>0.1660766791108991</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2318611987953855</v>
+        <v>0.2337611987953855</v>
       </c>
       <c r="C94">
-        <v>-205.2134073321436</v>
+        <v>-207.9774716963773</v>
       </c>
       <c r="D94">
-        <v>25.43059266785642</v>
+        <v>25.17352830362278</v>
       </c>
       <c r="E94">
-        <v>203.744</v>
+        <v>206.251</v>
       </c>
       <c r="F94">
-        <v>230.644</v>
+        <v>233.151</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8983,37 +8983,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M94">
-        <v>54.38585520000001</v>
+        <v>54.97700580000001</v>
       </c>
       <c r="N94">
-        <v>-45.35363297777779</v>
+        <v>-45.94478357777779</v>
       </c>
       <c r="O94">
-        <v>-9.342848393422225</v>
+        <v>-9.464625417022226</v>
       </c>
       <c r="P94">
-        <v>-36.01078458435556</v>
+        <v>-36.48015816075556</v>
       </c>
       <c r="Q94">
-        <v>-30.82078458435556</v>
+        <v>-31.29015816075556</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.2793371118757936</v>
+        <v>0.3126995564294785</v>
       </c>
       <c r="T94">
-        <v>5.393466786969832</v>
+        <v>6.163962042251236</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03421179589684521</v>
+        <v>0.03384392712376085</v>
       </c>
       <c r="W94">
-        <v>0.2277328585275239</v>
+        <v>0.2278196019842172</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1660766791108991</v>
+        <v>0.1642909083677712</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2337611987953855</v>
+        <v>0.2356611987953855</v>
       </c>
       <c r="C95">
-        <v>-207.9774716963773</v>
+        <v>-210.7363910147021</v>
       </c>
       <c r="D95">
-        <v>25.17352830362278</v>
+        <v>24.92160898529789</v>
       </c>
       <c r="E95">
-        <v>206.251</v>
+        <v>208.758</v>
       </c>
       <c r="F95">
-        <v>233.151</v>
+        <v>235.658</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9065,37 +9065,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M95">
-        <v>54.97700580000001</v>
+        <v>55.56815640000001</v>
       </c>
       <c r="N95">
-        <v>-45.94478357777779</v>
+        <v>-46.53593417777779</v>
       </c>
       <c r="O95">
-        <v>-9.464625417022226</v>
+        <v>-9.586402440622226</v>
       </c>
       <c r="P95">
-        <v>-36.48015816075556</v>
+        <v>-36.94953173715557</v>
       </c>
       <c r="Q95">
-        <v>-31.29015816075556</v>
+        <v>-31.75953173715557</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3126995564294785</v>
+        <v>0.3571828158343917</v>
       </c>
       <c r="T95">
-        <v>6.163962042251236</v>
+        <v>7.191289049293111</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03384392712376085</v>
+        <v>0.0334838853458485</v>
       </c>
       <c r="W95">
-        <v>0.2278196019842172</v>
+        <v>0.2279044998354489</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1642909083677712</v>
+        <v>0.1625431327468374</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2356611987953855</v>
+        <v>0.2375611987953855</v>
       </c>
       <c r="C96">
-        <v>-210.7363910147021</v>
+        <v>-213.4903182208811</v>
       </c>
       <c r="D96">
-        <v>24.92160898529789</v>
+        <v>24.67468177911895</v>
       </c>
       <c r="E96">
-        <v>208.758</v>
+        <v>211.265</v>
       </c>
       <c r="F96">
-        <v>235.658</v>
+        <v>238.165</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9147,37 +9147,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M96">
-        <v>55.56815640000001</v>
+        <v>56.15930700000001</v>
       </c>
       <c r="N96">
-        <v>-46.53593417777779</v>
+        <v>-47.12708477777778</v>
       </c>
       <c r="O96">
-        <v>-9.586402440622226</v>
+        <v>-9.708179464222225</v>
       </c>
       <c r="P96">
-        <v>-36.94953173715557</v>
+        <v>-37.41890531355556</v>
       </c>
       <c r="Q96">
-        <v>-31.75953173715557</v>
+        <v>-32.22890531355556</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3571828158343917</v>
+        <v>0.4194593790012702</v>
       </c>
       <c r="T96">
-        <v>7.191289049293111</v>
+        <v>8.629546859151738</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0334838853458485</v>
+        <v>0.03313142339483958</v>
       </c>
       <c r="W96">
-        <v>0.2279044998354489</v>
+        <v>0.2279876103634969</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1625431327468374</v>
+        <v>0.1608321524021339</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2375611987953855</v>
+        <v>0.2394611987953855</v>
       </c>
       <c r="C97">
-        <v>-213.4903182208811</v>
+        <v>-216.2394002469758</v>
       </c>
       <c r="D97">
-        <v>24.67468177911895</v>
+        <v>24.43259975302421</v>
       </c>
       <c r="E97">
-        <v>211.265</v>
+        <v>213.772</v>
       </c>
       <c r="F97">
-        <v>238.165</v>
+        <v>240.672</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9229,37 +9229,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M97">
-        <v>56.15930700000001</v>
+        <v>56.75045760000001</v>
       </c>
       <c r="N97">
-        <v>-47.12708477777778</v>
+        <v>-47.71823537777779</v>
       </c>
       <c r="O97">
-        <v>-9.708179464222225</v>
+        <v>-9.829956487822225</v>
       </c>
       <c r="P97">
-        <v>-37.41890531355556</v>
+        <v>-37.88827888995556</v>
       </c>
       <c r="Q97">
-        <v>-32.22890531355556</v>
+        <v>-32.69827888995557</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4194593790012702</v>
+        <v>0.5128742237515879</v>
       </c>
       <c r="T97">
-        <v>8.629546859151738</v>
+        <v>10.78693357393968</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03313142339483958</v>
+        <v>0.03278630440114333</v>
       </c>
       <c r="W97">
-        <v>0.2279876103634969</v>
+        <v>0.2280689894222104</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1608321524021339</v>
+        <v>0.1591568174812783</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2394611987953855</v>
+        <v>0.2413611987953855</v>
       </c>
       <c r="C98">
-        <v>-216.2394002469758</v>
+        <v>-218.9837783148988</v>
       </c>
       <c r="D98">
-        <v>24.43259975302421</v>
+        <v>24.19522168510125</v>
       </c>
       <c r="E98">
-        <v>213.772</v>
+        <v>216.279</v>
       </c>
       <c r="F98">
-        <v>240.672</v>
+        <v>243.179</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9311,37 +9311,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M98">
-        <v>56.7504576</v>
+        <v>57.3416082</v>
       </c>
       <c r="N98">
-        <v>-47.71823537777778</v>
+        <v>-48.30938597777778</v>
       </c>
       <c r="O98">
-        <v>-9.829956487822223</v>
+        <v>-9.951733511422223</v>
       </c>
       <c r="P98">
-        <v>-37.88827888995556</v>
+        <v>-38.35765246635556</v>
       </c>
       <c r="Q98">
-        <v>-32.69827888995556</v>
+        <v>-33.16765246635556</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5128742237515866</v>
+        <v>0.6685656316687821</v>
       </c>
       <c r="T98">
-        <v>10.78693357393965</v>
+        <v>14.3825780985862</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03278630440114334</v>
+        <v>0.03244830126298721</v>
       </c>
       <c r="W98">
-        <v>0.2280689894222104</v>
+        <v>0.2281486905621876</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1591568174812783</v>
+        <v>0.1575160255484817</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2413611987953855</v>
+        <v>0.2432611987953855</v>
       </c>
       <c r="C99">
-        <v>-218.9837783148988</v>
+        <v>-221.7235882111322</v>
       </c>
       <c r="D99">
-        <v>24.19522168510125</v>
+        <v>23.96241178886777</v>
       </c>
       <c r="E99">
-        <v>216.279</v>
+        <v>218.786</v>
       </c>
       <c r="F99">
-        <v>243.179</v>
+        <v>245.686</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9393,37 +9393,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M99">
-        <v>57.3416082</v>
+        <v>57.9327588</v>
       </c>
       <c r="N99">
-        <v>-48.30938597777778</v>
+        <v>-48.90053657777778</v>
       </c>
       <c r="O99">
-        <v>-9.951733511422223</v>
+        <v>-10.07351053502222</v>
       </c>
       <c r="P99">
-        <v>-38.35765246635556</v>
+        <v>-38.82702604275556</v>
       </c>
       <c r="Q99">
-        <v>-33.16765246635556</v>
+        <v>-33.63702604275556</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.6685656316687821</v>
+        <v>0.9799484475031732</v>
       </c>
       <c r="T99">
-        <v>14.3825780985862</v>
+        <v>21.57386714787929</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03244830126298721</v>
+        <v>0.03211719614805877</v>
       </c>
       <c r="W99">
-        <v>0.2281486905621876</v>
+        <v>0.2282267651482878</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1575160255484817</v>
+        <v>0.1559087191653339</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2432611987953855</v>
+        <v>0.2451611987953855</v>
       </c>
       <c r="C100">
-        <v>-221.7235882111322</v>
+        <v>-224.4589605457387</v>
       </c>
       <c r="D100">
-        <v>23.96241178886777</v>
+        <v>23.7340394542613</v>
       </c>
       <c r="E100">
-        <v>218.786</v>
+        <v>221.293</v>
       </c>
       <c r="F100">
-        <v>245.686</v>
+        <v>248.193</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9475,37 +9475,37 @@
         <v>9.032222222222224</v>
       </c>
       <c r="M100">
-        <v>57.9327588</v>
+        <v>58.52390940000001</v>
       </c>
       <c r="N100">
-        <v>-48.90053657777778</v>
+        <v>-49.49168717777778</v>
       </c>
       <c r="O100">
-        <v>-10.07351053502222</v>
+        <v>-10.19528755862222</v>
       </c>
       <c r="P100">
-        <v>-38.82702604275556</v>
+        <v>-39.29639961915556</v>
       </c>
       <c r="Q100">
-        <v>-33.63702604275556</v>
+        <v>-34.10639961915556</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>0.9799484475031732</v>
+        <v>1.914096895006347</v>
       </c>
       <c r="T100">
-        <v>21.57386714787929</v>
+        <v>43.14773429575859</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03211719614805877</v>
+        <v>0.0317927800253511</v>
       </c>
       <c r="W100">
-        <v>0.2282267651482878</v>
+        <v>0.2283032624700222</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1559087191653339</v>
+        <v>0.1543338836182092</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2451611987953855</v>
-      </c>
-      <c r="C101">
-        <v>-224.4589605457387</v>
-      </c>
-      <c r="D101">
-        <v>23.7340394542613</v>
-      </c>
-      <c r="E101">
-        <v>221.293</v>
-      </c>
-      <c r="F101">
-        <v>248.193</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>223.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>14.22222222222222</v>
-      </c>
-      <c r="K101">
-        <v>5.19</v>
-      </c>
-      <c r="L101">
-        <v>9.032222222222224</v>
-      </c>
-      <c r="M101">
-        <v>58.52390940000001</v>
-      </c>
-      <c r="N101">
-        <v>-49.49168717777778</v>
-      </c>
-      <c r="O101">
-        <v>-10.19528755862222</v>
-      </c>
-      <c r="P101">
-        <v>-39.29639961915556</v>
-      </c>
-      <c r="Q101">
-        <v>-34.10639961915556</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>1.914096895006347</v>
-      </c>
-      <c r="T101">
-        <v>43.14773429575859</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.0317927800253511</v>
-      </c>
-      <c r="W101">
-        <v>0.2283032624700222</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1543338836182092</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
